--- a/research/traditional_assets/database/data/gibraltar/gibraltar_food_processing.xlsx
+++ b/research/traditional_assets/database/data/gibraltar/gibraltar_food_processing.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.02509299966181941</v>
+        <v>0.01323109843081312</v>
       </c>
       <c r="H2">
-        <v>0.02509299966181941</v>
+        <v>0.01323109843081312</v>
       </c>
       <c r="I2">
-        <v>-0.003648797855530085</v>
+        <v>-0.009928396734138324</v>
       </c>
       <c r="J2">
-        <v>-0.003648797855530085</v>
+        <v>-0.009928396734138324</v>
       </c>
       <c r="K2">
-        <v>-16</v>
+        <v>-19.5</v>
       </c>
       <c r="L2">
-        <v>-0.05410889414947583</v>
+        <v>-0.06954350927246791</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>12.3</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04320337197049526</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.6307692307692309</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,76 +624,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>12.3</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>20.7</v>
+        <v>25.2</v>
       </c>
       <c r="V2">
-        <v>0.06950973807924782</v>
+        <v>0.08851422550052687</v>
       </c>
       <c r="W2">
-        <v>-0.3082851637764933</v>
+        <v>-0.3907815631262525</v>
       </c>
       <c r="X2">
-        <v>0.1155682921799384</v>
+        <v>0.1385025294193186</v>
       </c>
       <c r="Y2">
-        <v>-0.4238534559564317</v>
+        <v>-0.5292840925455711</v>
       </c>
       <c r="Z2">
-        <v>1.577447377244347</v>
+        <v>1.597451258802673</v>
       </c>
       <c r="AA2">
-        <v>-0.005755786607300731</v>
+        <v>-0.01586012986084162</v>
       </c>
       <c r="AB2">
-        <v>0.08943597928265629</v>
+        <v>0.09950394414088685</v>
       </c>
       <c r="AC2">
-        <v>-0.09519176588995702</v>
+        <v>-0.1153640740017285</v>
       </c>
       <c r="AD2">
-        <v>192.1</v>
+        <v>204.4</v>
       </c>
       <c r="AE2">
-        <v>2.154747629401232</v>
+        <v>1.22961222126193</v>
       </c>
       <c r="AF2">
-        <v>194.2547476294012</v>
+        <v>205.6296122212619</v>
       </c>
       <c r="AG2">
-        <v>173.5547476294012</v>
+        <v>180.4296122212619</v>
       </c>
       <c r="AH2">
-        <v>0.3947827931043706</v>
+        <v>0.4193701687518544</v>
       </c>
       <c r="AI2">
-        <v>0.7740628518264494</v>
+        <v>0.8566843495614628</v>
       </c>
       <c r="AJ2">
-        <v>0.3682040936306793</v>
+        <v>0.3879125462677093</v>
       </c>
       <c r="AK2">
-        <v>0.7537510058586954</v>
+        <v>0.8398730992235371</v>
       </c>
       <c r="AL2">
-        <v>11.8</v>
+        <v>14.2</v>
       </c>
       <c r="AM2">
-        <v>11.526</v>
+        <v>14.111</v>
       </c>
       <c r="AN2">
-        <v>49.48480164863472</v>
+        <v>84.04605263157895</v>
       </c>
       <c r="AO2">
-        <v>-0.1228813559322034</v>
+        <v>-0.226056338028169</v>
       </c>
       <c r="AP2">
-        <v>44.707559925142</v>
+        <v>74.18980765676889</v>
       </c>
       <c r="AQ2">
-        <v>-0.1258025334027416</v>
+        <v>-0.2274821061583162</v>
       </c>
     </row>
     <row r="3">
@@ -713,31 +716,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.02509299966181941</v>
+        <v>0.01323109843081312</v>
       </c>
       <c r="H3">
-        <v>0.02509299966181941</v>
+        <v>0.01323109843081312</v>
       </c>
       <c r="I3">
-        <v>-0.003648797855530085</v>
+        <v>-0.009928396734138324</v>
       </c>
       <c r="J3">
-        <v>-0.003648797855530085</v>
+        <v>-0.009928396734138324</v>
       </c>
       <c r="K3">
-        <v>-16</v>
+        <v>-19.5</v>
       </c>
       <c r="L3">
-        <v>-0.05410889414947583</v>
+        <v>-0.06954350927246791</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>12.3</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.04320337197049526</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.6307692307692309</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,76 +752,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>12.3</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>20.7</v>
+        <v>25.2</v>
       </c>
       <c r="V3">
-        <v>0.06950973807924782</v>
+        <v>0.08851422550052687</v>
       </c>
       <c r="W3">
-        <v>-0.3082851637764933</v>
+        <v>-0.3907815631262525</v>
       </c>
       <c r="X3">
-        <v>0.1155682921799384</v>
+        <v>0.1385025294193186</v>
       </c>
       <c r="Y3">
-        <v>-0.4238534559564317</v>
+        <v>-0.5292840925455711</v>
       </c>
       <c r="Z3">
-        <v>1.577447377244347</v>
+        <v>1.597451258802673</v>
       </c>
       <c r="AA3">
-        <v>-0.005755786607300731</v>
+        <v>-0.01586012986084162</v>
       </c>
       <c r="AB3">
-        <v>0.08943597928265629</v>
+        <v>0.09950394414088685</v>
       </c>
       <c r="AC3">
-        <v>-0.09519176588995702</v>
+        <v>-0.1153640740017285</v>
       </c>
       <c r="AD3">
-        <v>192.1</v>
+        <v>204.4</v>
       </c>
       <c r="AE3">
-        <v>2.154747629401232</v>
+        <v>1.22961222126193</v>
       </c>
       <c r="AF3">
-        <v>194.2547476294012</v>
+        <v>205.6296122212619</v>
       </c>
       <c r="AG3">
-        <v>173.5547476294012</v>
+        <v>180.4296122212619</v>
       </c>
       <c r="AH3">
-        <v>0.3947827931043706</v>
+        <v>0.4193701687518544</v>
       </c>
       <c r="AI3">
-        <v>0.7740628518264494</v>
+        <v>0.8566843495614628</v>
       </c>
       <c r="AJ3">
-        <v>0.3682040936306793</v>
+        <v>0.3879125462677093</v>
       </c>
       <c r="AK3">
-        <v>0.7537510058586954</v>
+        <v>0.8398730992235371</v>
       </c>
       <c r="AL3">
-        <v>11.8</v>
+        <v>14.2</v>
       </c>
       <c r="AM3">
-        <v>11.526</v>
+        <v>14.111</v>
       </c>
       <c r="AN3">
-        <v>49.48480164863472</v>
+        <v>84.04605263157895</v>
       </c>
       <c r="AO3">
-        <v>-0.1228813559322034</v>
+        <v>-0.226056338028169</v>
       </c>
       <c r="AP3">
-        <v>44.707559925142</v>
+        <v>74.18980765676889</v>
       </c>
       <c r="AQ3">
-        <v>-0.1258025334027416</v>
+        <v>-0.2274821061583162</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/gibraltar/gibraltar_food_processing.xlsx
+++ b/research/traditional_assets/database/data/gibraltar/gibraltar_food_processing.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07933427694422543</v>
+        <v>0.07917157568197034</v>
       </c>
       <c r="C2">
-        <v>424.2185203694597</v>
+        <v>421.4252915178776</v>
       </c>
       <c r="D2">
-        <v>400.2185203694597</v>
+        <v>402.1697635190949</v>
       </c>
       <c r="E2">
-        <v>-198.9472001217346</v>
+        <v>-194.2027281205172</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.744472001217345</v>
       </c>
       <c r="G2">
         <v>24</v>
@@ -1433,28 +1433,28 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2386469416612325</v>
       </c>
       <c r="N2">
-        <v>8.745999999999999</v>
+        <v>8.507353058338767</v>
       </c>
       <c r="O2">
-        <v>2.166840707520568</v>
+        <v>2.107715403619717</v>
       </c>
       <c r="P2">
-        <v>6.579159292479431</v>
+        <v>6.39963765471905</v>
       </c>
       <c r="Q2">
-        <v>11.60915929247943</v>
+        <v>11.42963765471905</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07933427694422543</v>
+        <v>0.07958908589558926</v>
       </c>
       <c r="T2">
-        <v>0.6158190843120042</v>
+        <v>0.6204983626326419</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>36.64828025500216</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07917157568197034</v>
+        <v>0.07900887441971526</v>
       </c>
       <c r="C3">
-        <v>421.4252915178776</v>
+        <v>418.6511822377327</v>
       </c>
       <c r="D3">
-        <v>402.1697635190949</v>
+        <v>404.1401262401674</v>
       </c>
       <c r="E3">
-        <v>-194.2027281205172</v>
+        <v>-189.4582561192999</v>
       </c>
       <c r="F3">
-        <v>4.744472001217345</v>
+        <v>9.488944002434691</v>
       </c>
       <c r="G3">
         <v>24</v>
@@ -1515,28 +1515,28 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M3">
-        <v>0.2386469416612325</v>
+        <v>0.4772938833224649</v>
       </c>
       <c r="N3">
-        <v>8.507353058338767</v>
+        <v>8.268706116677533</v>
       </c>
       <c r="O3">
-        <v>2.107715403619717</v>
+        <v>2.048590099718866</v>
       </c>
       <c r="P3">
-        <v>6.39963765471905</v>
+        <v>6.220116016958668</v>
       </c>
       <c r="Q3">
-        <v>11.42963765471905</v>
+        <v>11.25011601695867</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07958908589558926</v>
+        <v>0.079849095029634</v>
       </c>
       <c r="T3">
-        <v>0.6204983626326419</v>
+        <v>0.6252731364292111</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>36.64828025500216</v>
+        <v>18.32414012750108</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07900887441971526</v>
+        <v>0.07888002430863345</v>
       </c>
       <c r="C4">
-        <v>418.6511822377327</v>
+        <v>415.4808777665274</v>
       </c>
       <c r="D4">
-        <v>404.1401262401674</v>
+        <v>405.7142937701794</v>
       </c>
       <c r="E4">
-        <v>-189.4582561192999</v>
+        <v>-184.7137841180825</v>
       </c>
       <c r="F4">
-        <v>9.488944002434691</v>
+        <v>14.23341600365204</v>
       </c>
       <c r="G4">
         <v>24</v>
@@ -1597,45 +1597,45 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M4">
-        <v>0.4772938833224649</v>
+        <v>0.7372909489891755</v>
       </c>
       <c r="N4">
-        <v>8.268706116677533</v>
+        <v>8.008709051010824</v>
       </c>
       <c r="O4">
-        <v>2.048590099718866</v>
+        <v>1.9841752557076</v>
       </c>
       <c r="P4">
-        <v>6.220116016958668</v>
+        <v>6.024533795303223</v>
       </c>
       <c r="Q4">
-        <v>11.25011601695867</v>
+        <v>11.05453379530322</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.079849095029634</v>
+        <v>0.0801144651767518</v>
       </c>
       <c r="T4">
-        <v>0.6252731364292111</v>
+        <v>0.6301463591700395</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.2477521961491617</v>
       </c>
       <c r="W4">
-        <v>0.03783806453369716</v>
+        <v>0.03896643623947342</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>18.32414012750108</v>
+        <v>11.86234553942477</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07888002430863345</v>
+        <v>0.07877975961409797</v>
       </c>
       <c r="C5">
-        <v>415.4808777665274</v>
+        <v>411.9698538016067</v>
       </c>
       <c r="D5">
-        <v>405.7142937701794</v>
+        <v>406.9477418064761</v>
       </c>
       <c r="E5">
-        <v>-184.7137841180825</v>
+        <v>-179.9693121168652</v>
       </c>
       <c r="F5">
-        <v>14.23341600365204</v>
+        <v>18.97788800486938</v>
       </c>
       <c r="G5">
         <v>24</v>
@@ -1679,45 +1679,45 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M5">
-        <v>0.7372909489891755</v>
+        <v>1.015317008260512</v>
       </c>
       <c r="N5">
-        <v>8.008709051010824</v>
+        <v>7.730682991739487</v>
       </c>
       <c r="O5">
-        <v>1.9841752557076</v>
+        <v>1.91529368893643</v>
       </c>
       <c r="P5">
-        <v>6.024533795303223</v>
+        <v>5.815389302803057</v>
       </c>
       <c r="Q5">
-        <v>11.05453379530322</v>
+        <v>10.84538930280306</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0801144651767518</v>
+        <v>0.08038536386860123</v>
       </c>
       <c r="T5">
-        <v>0.6301463591700395</v>
+        <v>0.635121107384635</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.2477521961491617</v>
       </c>
       <c r="W5">
-        <v>0.03896643623947342</v>
+        <v>0.04024525750601984</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>11.86234553942477</v>
+        <v>8.614058396386023</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07877975961409797</v>
+        <v>0.07867122019372015</v>
       </c>
       <c r="C6">
-        <v>411.9698538016067</v>
+        <v>408.569106546822</v>
       </c>
       <c r="D6">
-        <v>406.9477418064761</v>
+        <v>408.2914665529087</v>
       </c>
       <c r="E6">
-        <v>-179.9693121168652</v>
+        <v>-175.2248401156479</v>
       </c>
       <c r="F6">
-        <v>18.97788800486938</v>
+        <v>23.72236000608673</v>
       </c>
       <c r="G6">
         <v>24</v>
@@ -1761,45 +1761,45 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M6">
-        <v>1.015317008260512</v>
+        <v>1.288124148330509</v>
       </c>
       <c r="N6">
-        <v>7.730682991739487</v>
+        <v>7.457875851669489</v>
       </c>
       <c r="O6">
-        <v>1.91529368893643</v>
+        <v>1.847705120858916</v>
       </c>
       <c r="P6">
-        <v>5.815389302803057</v>
+        <v>5.610170730810573</v>
       </c>
       <c r="Q6">
-        <v>10.84538930280306</v>
+        <v>10.64017073081057</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08038536386860123</v>
+        <v>0.0806619656908054</v>
       </c>
       <c r="T6">
-        <v>0.635121107384635</v>
+        <v>0.6402005871405905</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.2477521961491617</v>
       </c>
       <c r="W6">
-        <v>0.04024525750601984</v>
+        <v>0.04084705574910052</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>8.614058396386023</v>
+        <v>6.789718220355832</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07867122019372015</v>
+        <v>0.07858374371185015</v>
       </c>
       <c r="C7">
-        <v>408.569106546822</v>
+        <v>404.91407391487</v>
       </c>
       <c r="D7">
-        <v>408.2914665529087</v>
+        <v>409.380905922174</v>
       </c>
       <c r="E7">
-        <v>-175.2248401156479</v>
+        <v>-170.4803681144305</v>
       </c>
       <c r="F7">
-        <v>23.72236000608673</v>
+        <v>28.46683200730408</v>
       </c>
       <c r="G7">
         <v>24</v>
@@ -1843,45 +1843,45 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M7">
-        <v>1.288124148330509</v>
+        <v>1.574215810003916</v>
       </c>
       <c r="N7">
-        <v>7.457875851669489</v>
+        <v>7.171784189996083</v>
       </c>
       <c r="O7">
-        <v>1.847705120858916</v>
+        <v>1.776825283379367</v>
       </c>
       <c r="P7">
-        <v>5.610170730810573</v>
+        <v>5.394958906616717</v>
       </c>
       <c r="Q7">
-        <v>10.64017073081057</v>
+        <v>10.42495890661672</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0806619656908054</v>
+        <v>0.08094445265816284</v>
       </c>
       <c r="T7">
-        <v>0.6402005871405905</v>
+        <v>0.6453881409339067</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.2477521961491617</v>
       </c>
       <c r="W7">
-        <v>0.04084705574910052</v>
+        <v>0.04159930355295136</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>6.789718220355832</v>
+        <v>5.555782088085016</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07858374371185015</v>
+        <v>0.0784586548397876</v>
       </c>
       <c r="C8">
-        <v>404.91407391487</v>
+        <v>401.7376088023919</v>
       </c>
       <c r="D8">
-        <v>409.380905922174</v>
+        <v>410.9489128109133</v>
       </c>
       <c r="E8">
-        <v>-170.4803681144305</v>
+        <v>-165.7358961132132</v>
       </c>
       <c r="F8">
-        <v>28.46683200730407</v>
+        <v>33.21130400852142</v>
       </c>
       <c r="G8">
         <v>24</v>
@@ -1925,28 +1925,28 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M8">
-        <v>1.574215810003915</v>
+        <v>1.836585111671234</v>
       </c>
       <c r="N8">
-        <v>7.171784189996083</v>
+        <v>6.909414888328764</v>
       </c>
       <c r="O8">
-        <v>1.776825283379367</v>
+        <v>1.711822712689166</v>
       </c>
       <c r="P8">
-        <v>5.394958906616717</v>
+        <v>5.197592175639598</v>
       </c>
       <c r="Q8">
-        <v>10.42495890661672</v>
+        <v>10.2275921756396</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08094445265816284</v>
+        <v>0.0812330146140656</v>
       </c>
       <c r="T8">
-        <v>0.6453881409339067</v>
+        <v>0.6506872550238533</v>
       </c>
       <c r="U8">
         <v>0.0553</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>5.555782088085016</v>
+        <v>4.7620989326443</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07845865483978759</v>
+        <v>0.07869464491357345</v>
       </c>
       <c r="C9">
-        <v>401.7376088023921</v>
+        <v>394.0449406886686</v>
       </c>
       <c r="D9">
-        <v>410.9489128109135</v>
+        <v>408.0007166984074</v>
       </c>
       <c r="E9">
-        <v>-165.7358961132131</v>
+        <v>-160.9914241119958</v>
       </c>
       <c r="F9">
-        <v>33.21130400852142</v>
+        <v>37.95577600973876</v>
       </c>
       <c r="G9">
         <v>24</v>
@@ -2007,45 +2007,45 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M9">
-        <v>1.836585111671235</v>
+        <v>2.326689069396986</v>
       </c>
       <c r="N9">
-        <v>6.909414888328763</v>
+        <v>6.419310930603013</v>
       </c>
       <c r="O9">
-        <v>1.711822712689166</v>
+        <v>1.590398380821215</v>
       </c>
       <c r="P9">
-        <v>5.197592175639597</v>
+        <v>4.828912549781798</v>
       </c>
       <c r="Q9">
-        <v>10.2275921756396</v>
+        <v>9.858912549781799</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0812330146140656</v>
+        <v>0.08152784965596624</v>
       </c>
       <c r="T9">
-        <v>0.6506872550238533</v>
+        <v>0.6561015672461902</v>
       </c>
       <c r="U9">
-        <v>0.0553</v>
+        <v>0.0613</v>
       </c>
       <c r="V9">
         <v>0.2477521961491617</v>
       </c>
       <c r="W9">
-        <v>0.04159930355295136</v>
+        <v>0.04611279037605638</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.7620989326443</v>
+        <v>3.758989593855238</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07869464491357345</v>
+        <v>0.07880425735631237</v>
       </c>
       <c r="C10">
-        <v>394.0449406886686</v>
+        <v>387.9454327381879</v>
       </c>
       <c r="D10">
-        <v>408.0007166984074</v>
+        <v>406.645680749144</v>
       </c>
       <c r="E10">
-        <v>-160.9914241119958</v>
+        <v>-156.2469521107785</v>
       </c>
       <c r="F10">
-        <v>37.95577600973876</v>
+        <v>42.70024801095611</v>
       </c>
       <c r="G10">
         <v>24</v>
@@ -2089,45 +2089,45 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M10">
-        <v>2.326689069396986</v>
+        <v>2.737085897502287</v>
       </c>
       <c r="N10">
-        <v>6.419310930603013</v>
+        <v>6.008914102497712</v>
       </c>
       <c r="O10">
-        <v>1.590398380821215</v>
+        <v>1.488721665365477</v>
       </c>
       <c r="P10">
-        <v>4.828912549781798</v>
+        <v>4.520192437132235</v>
       </c>
       <c r="Q10">
-        <v>9.858912549781799</v>
+        <v>9.550192437132235</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08152784965596624</v>
+        <v>0.08182916458889768</v>
       </c>
       <c r="T10">
-        <v>0.6561015672461902</v>
+        <v>0.6616348753415454</v>
       </c>
       <c r="U10">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V10">
         <v>0.2477521961491617</v>
       </c>
       <c r="W10">
-        <v>0.04611279037605638</v>
+        <v>0.04821908422683873</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.758989593855238</v>
+        <v>3.195369209267826</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07880425735631237</v>
+        <v>0.07933211957799234</v>
       </c>
       <c r="C11">
-        <v>387.9454327381879</v>
+        <v>376.7995493386381</v>
       </c>
       <c r="D11">
-        <v>406.645680749144</v>
+        <v>400.2442693508116</v>
       </c>
       <c r="E11">
-        <v>-156.2469521107785</v>
+        <v>-151.5024801095611</v>
       </c>
       <c r="F11">
-        <v>42.70024801095611</v>
+        <v>47.44472001217346</v>
       </c>
       <c r="G11">
         <v>24</v>
@@ -2171,45 +2171,45 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M11">
-        <v>2.737085897502287</v>
+        <v>3.411275368875271</v>
       </c>
       <c r="N11">
-        <v>6.008914102497712</v>
+        <v>5.334724631124727</v>
       </c>
       <c r="O11">
-        <v>1.488721665365477</v>
+        <v>1.321689743212178</v>
       </c>
       <c r="P11">
-        <v>4.520192437132235</v>
+        <v>4.01303488791255</v>
       </c>
       <c r="Q11">
-        <v>9.550192437132235</v>
+        <v>9.043034887912551</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08182916458889768</v>
+        <v>0.08213717540922758</v>
       </c>
       <c r="T11">
-        <v>0.6616348753415454</v>
+        <v>0.6672911458390196</v>
       </c>
       <c r="U11">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V11">
         <v>0.2477521961491617</v>
       </c>
       <c r="W11">
-        <v>0.04821908422683873</v>
+        <v>0.05408661709687528</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>3.195369209267826</v>
+        <v>2.563850482373586</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07933211957799234</v>
+        <v>0.07965461814922105</v>
       </c>
       <c r="C12">
-        <v>376.7995493386381</v>
+        <v>368.2423565901603</v>
       </c>
       <c r="D12">
-        <v>400.2442693508116</v>
+        <v>396.4315486035511</v>
       </c>
       <c r="E12">
-        <v>-151.5024801095611</v>
+        <v>-146.7580081083438</v>
       </c>
       <c r="F12">
-        <v>47.44472001217346</v>
+        <v>52.1891920133908</v>
       </c>
       <c r="G12">
         <v>24</v>
@@ -2253,45 +2253,45 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M12">
-        <v>3.411275368875272</v>
+        <v>3.955940754615023</v>
       </c>
       <c r="N12">
-        <v>5.334724631124726</v>
+        <v>4.790059245384976</v>
       </c>
       <c r="O12">
-        <v>1.321689743212177</v>
+        <v>1.186747697728724</v>
       </c>
       <c r="P12">
-        <v>4.013034887912549</v>
+        <v>3.603311547656252</v>
       </c>
       <c r="Q12">
-        <v>9.043034887912549</v>
+        <v>8.633311547656252</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08213717540922758</v>
+        <v>0.08245210782102558</v>
       </c>
       <c r="T12">
-        <v>0.6672911458390196</v>
+        <v>0.6730745235386844</v>
       </c>
       <c r="U12">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V12">
         <v>0.2477521961491617</v>
       </c>
       <c r="W12">
-        <v>0.05408661709687528</v>
+        <v>0.05702038353189354</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y12">
-        <v>2.563850482373586</v>
+        <v>2.210852119005287</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07965461814922105</v>
+        <v>0.07968374007694794</v>
       </c>
       <c r="C13">
-        <v>368.2423565901603</v>
+        <v>363.1571650910105</v>
       </c>
       <c r="D13">
-        <v>396.4315486035511</v>
+        <v>396.0908291056186</v>
       </c>
       <c r="E13">
-        <v>-146.7580081083438</v>
+        <v>-142.0135361071264</v>
       </c>
       <c r="F13">
-        <v>52.1891920133908</v>
+        <v>56.93366401460815</v>
       </c>
       <c r="G13">
         <v>24</v>
@@ -2335,28 +2335,28 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M13">
-        <v>3.955940754615023</v>
+        <v>4.315571732307298</v>
       </c>
       <c r="N13">
-        <v>4.790059245384976</v>
+        <v>4.430428267692701</v>
       </c>
       <c r="O13">
-        <v>1.186747697728724</v>
+        <v>1.097648333202193</v>
       </c>
       <c r="P13">
-        <v>3.603311547656252</v>
+        <v>3.332779934490508</v>
       </c>
       <c r="Q13">
-        <v>8.633311547656252</v>
+        <v>8.362779934490508</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08245210782102558</v>
+        <v>0.08277419778763717</v>
       </c>
       <c r="T13">
-        <v>0.6730745235386844</v>
+        <v>0.6789893416406141</v>
       </c>
       <c r="U13">
         <v>0.07580000000000001</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>2.210852119005287</v>
+        <v>2.026614442421513</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07968374007694794</v>
+        <v>0.08110151145058345</v>
       </c>
       <c r="C14">
-        <v>363.1571650910105</v>
+        <v>342.5049821791256</v>
       </c>
       <c r="D14">
-        <v>396.0908291056186</v>
+        <v>380.1831181949511</v>
       </c>
       <c r="E14">
-        <v>-142.0135361071264</v>
+        <v>-137.2690641059091</v>
       </c>
       <c r="F14">
-        <v>56.93366401460815</v>
+        <v>61.67813601582549</v>
       </c>
       <c r="G14">
         <v>24</v>
@@ -2417,45 +2417,45 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M14">
-        <v>4.315571732307298</v>
+        <v>5.551032241424294</v>
       </c>
       <c r="N14">
-        <v>4.430428267692701</v>
+        <v>3.194967758575705</v>
       </c>
       <c r="O14">
-        <v>1.097648333202193</v>
+        <v>0.7915602788128955</v>
       </c>
       <c r="P14">
-        <v>3.332779934490508</v>
+        <v>2.403407479762809</v>
       </c>
       <c r="Q14">
-        <v>8.362779934490508</v>
+        <v>7.43340747976281</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08277419778763717</v>
+        <v>0.08310369212129728</v>
       </c>
       <c r="T14">
-        <v>0.6789893416406141</v>
+        <v>0.6850401325724732</v>
       </c>
       <c r="U14">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V14">
         <v>0.2477521961491617</v>
       </c>
       <c r="W14">
-        <v>0.05702038353189354</v>
+        <v>0.06770230234657544</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y14">
-        <v>2.026614442421513</v>
+        <v>1.57556281780052</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08110151145058345</v>
+        <v>0.08786390925002004</v>
       </c>
       <c r="C15">
-        <v>342.5049821791256</v>
+        <v>276.6404305727714</v>
       </c>
       <c r="D15">
-        <v>380.1831181949511</v>
+        <v>319.0630385898143</v>
       </c>
       <c r="E15">
-        <v>-137.2690641059091</v>
+        <v>-132.5245921046917</v>
       </c>
       <c r="F15">
-        <v>61.67813601582549</v>
+        <v>66.42260801704285</v>
       </c>
       <c r="G15">
         <v>24</v>
@@ -2499,45 +2499,45 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M15">
-        <v>5.551032241424294</v>
+        <v>9.750838856901892</v>
       </c>
       <c r="N15">
-        <v>3.194967758575705</v>
+        <v>-1.004838856901893</v>
       </c>
       <c r="O15">
-        <v>0.7915602788128955</v>
+        <v>-0.2489510335734572</v>
       </c>
       <c r="P15">
-        <v>2.403407479762809</v>
+        <v>-0.7558878233284356</v>
       </c>
       <c r="Q15">
-        <v>7.43340747976281</v>
+        <v>4.274112176671565</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08310369212129728</v>
+        <v>0.08358022591268396</v>
       </c>
       <c r="T15">
-        <v>0.6850401325724732</v>
+        <v>0.693791136911811</v>
       </c>
       <c r="U15">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V15">
-        <v>0.2477521961491617</v>
+        <v>0.2222209534297475</v>
       </c>
       <c r="W15">
-        <v>0.06770230234657544</v>
+        <v>0.1141779640365131</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y15">
-        <v>1.57556281780052</v>
+        <v>0.8969484706240795</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08786390925002004</v>
+        <v>0.08887390925002005</v>
       </c>
       <c r="C16">
-        <v>276.6404305727714</v>
+        <v>264.4145463991596</v>
       </c>
       <c r="D16">
-        <v>319.0630385898143</v>
+        <v>311.5816264174198</v>
       </c>
       <c r="E16">
-        <v>-132.5245921046917</v>
+        <v>-127.7801201034744</v>
       </c>
       <c r="F16">
-        <v>66.42260801704285</v>
+        <v>71.16708001826019</v>
       </c>
       <c r="G16">
         <v>24</v>
@@ -2581,37 +2581,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M16">
-        <v>9.750838856901892</v>
+        <v>10.4473273466806</v>
       </c>
       <c r="N16">
-        <v>-1.004838856901893</v>
+        <v>-1.701327346680598</v>
       </c>
       <c r="O16">
-        <v>-0.2489510335734572</v>
+        <v>-0.4215075865087444</v>
       </c>
       <c r="P16">
-        <v>-0.7558878233284356</v>
+        <v>-1.279819760171854</v>
       </c>
       <c r="Q16">
-        <v>4.274112176671565</v>
+        <v>3.750180239828147</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08358022591268396</v>
+        <v>0.08402469915871555</v>
       </c>
       <c r="T16">
-        <v>0.693791136911811</v>
+        <v>0.7019533855813618</v>
       </c>
       <c r="U16">
         <v>0.1468</v>
       </c>
       <c r="V16">
-        <v>0.2222209534297475</v>
+        <v>0.2074062232010977</v>
       </c>
       <c r="W16">
-        <v>0.1141779640365131</v>
+        <v>0.1163527664340789</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.8969484706240795</v>
+        <v>0.8371519059158076</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08887390925002003</v>
+        <v>0.09880447331178861</v>
       </c>
       <c r="C17">
-        <v>264.4145463991597</v>
+        <v>201.294222167371</v>
       </c>
       <c r="D17">
-        <v>311.5816264174198</v>
+        <v>253.2057741868485</v>
       </c>
       <c r="E17">
-        <v>-127.7801201034744</v>
+        <v>-123.035648102257</v>
       </c>
       <c r="F17">
-        <v>71.16708001826018</v>
+        <v>75.91155201947753</v>
       </c>
       <c r="G17">
         <v>24</v>
@@ -2663,45 +2663,45 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M17">
-        <v>10.44732734668059</v>
+        <v>15.24303964551109</v>
       </c>
       <c r="N17">
-        <v>-1.701327346680596</v>
+        <v>-6.497039645511089</v>
       </c>
       <c r="O17">
-        <v>-0.4215075865087439</v>
+        <v>-1.609655840643544</v>
       </c>
       <c r="P17">
-        <v>-1.279819760171852</v>
+        <v>-4.887383804867546</v>
       </c>
       <c r="Q17">
-        <v>3.750180239828148</v>
+        <v>0.1426161951324545</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08402469915871555</v>
+        <v>0.08481375993651999</v>
       </c>
       <c r="T17">
-        <v>0.7019533855813618</v>
+        <v>0.7164435947026807</v>
       </c>
       <c r="U17">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.2074062232010978</v>
+        <v>0.1421527961556329</v>
       </c>
       <c r="W17">
-        <v>0.1163527664340789</v>
+        <v>0.1722557185319489</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y17">
-        <v>0.8371519059158077</v>
+        <v>0.5737700749584813</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09880447331178861</v>
+        <v>0.1003544733117886</v>
       </c>
       <c r="C18">
-        <v>201.294222167371</v>
+        <v>189.3556755804349</v>
       </c>
       <c r="D18">
-        <v>253.2057741868485</v>
+        <v>246.0116996011297</v>
       </c>
       <c r="E18">
-        <v>-123.035648102257</v>
+        <v>-118.2911761010397</v>
       </c>
       <c r="F18">
-        <v>75.91155201947753</v>
+        <v>80.65602402069489</v>
       </c>
       <c r="G18">
         <v>24</v>
@@ -2745,37 +2745,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M18">
-        <v>15.24303964551109</v>
+        <v>16.19572962335553</v>
       </c>
       <c r="N18">
-        <v>-6.497039645511089</v>
+        <v>-7.449729623355534</v>
       </c>
       <c r="O18">
-        <v>-1.609655840643544</v>
+        <v>-1.845686874903801</v>
       </c>
       <c r="P18">
-        <v>-4.887383804867546</v>
+        <v>-5.604042748451733</v>
       </c>
       <c r="Q18">
-        <v>0.1426161951324545</v>
+        <v>-0.574042748451733</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08481375993651999</v>
+        <v>0.08528380523695998</v>
       </c>
       <c r="T18">
-        <v>0.7164435947026807</v>
+        <v>0.7250754452412671</v>
       </c>
       <c r="U18">
         <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.1421527961556329</v>
+        <v>0.1337908669700074</v>
       </c>
       <c r="W18">
-        <v>0.1722557185319489</v>
+        <v>0.1739347939124225</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.5737700749584813</v>
+        <v>0.5400188940785706</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1003544733117886</v>
+        <v>0.1019044733117886</v>
       </c>
       <c r="C19">
-        <v>189.3556755804349</v>
+        <v>177.8146308306836</v>
       </c>
       <c r="D19">
-        <v>246.0116996011297</v>
+        <v>239.2151268525958</v>
       </c>
       <c r="E19">
-        <v>-118.2911761010397</v>
+        <v>-113.5467040998223</v>
       </c>
       <c r="F19">
-        <v>80.65602402069489</v>
+        <v>85.40049602191223</v>
       </c>
       <c r="G19">
         <v>24</v>
@@ -2827,37 +2827,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M19">
-        <v>16.19572962335553</v>
+        <v>17.14841960119998</v>
       </c>
       <c r="N19">
-        <v>-7.449729623355534</v>
+        <v>-8.402419601199977</v>
       </c>
       <c r="O19">
-        <v>-1.845686874903801</v>
+        <v>-2.081717909164058</v>
       </c>
       <c r="P19">
-        <v>-5.604042748451733</v>
+        <v>-6.320701692035919</v>
       </c>
       <c r="Q19">
-        <v>-0.574042748451733</v>
+        <v>-1.290701692035919</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08528380523695998</v>
+        <v>0.08576531505692292</v>
       </c>
       <c r="T19">
-        <v>0.7250754452412671</v>
+        <v>0.7339178287198193</v>
       </c>
       <c r="U19">
         <v>0.2008</v>
       </c>
       <c r="V19">
-        <v>0.1337908669700074</v>
+        <v>0.1263580410272292</v>
       </c>
       <c r="W19">
-        <v>0.1739347939124225</v>
+        <v>0.1754273053617324</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.5400188940785706</v>
+        <v>0.5100178444075388</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1019044733117886</v>
+        <v>0.1102176842995503</v>
       </c>
       <c r="C20">
-        <v>177.8146308306836</v>
+        <v>142.199042572906</v>
       </c>
       <c r="D20">
-        <v>239.2151268525958</v>
+        <v>208.3440105960356</v>
       </c>
       <c r="E20">
-        <v>-113.5467040998223</v>
+        <v>-108.802232098605</v>
       </c>
       <c r="F20">
-        <v>85.40049602191222</v>
+        <v>90.14496802312956</v>
       </c>
       <c r="G20">
         <v>24</v>
@@ -2909,45 +2909,45 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M20">
-        <v>17.14841960119998</v>
+        <v>21.25618345985395</v>
       </c>
       <c r="N20">
-        <v>-8.402419601199977</v>
+        <v>-12.51018345985395</v>
       </c>
       <c r="O20">
-        <v>-2.081717909164058</v>
+        <v>-3.099425426407735</v>
       </c>
       <c r="P20">
-        <v>-6.320701692035919</v>
+        <v>-9.410758033446218</v>
       </c>
       <c r="Q20">
-        <v>-1.290701692035919</v>
+        <v>-4.380758033446218</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08576531505692292</v>
+        <v>0.08639848065980058</v>
       </c>
       <c r="T20">
-        <v>0.7339178287198193</v>
+        <v>0.7455451991990004</v>
       </c>
       <c r="U20">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.1263580410272292</v>
+        <v>0.1019393115237751</v>
       </c>
       <c r="W20">
-        <v>0.1754273053617324</v>
+        <v>0.2117627103426938</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y20">
-        <v>0.5100178444075388</v>
+        <v>0.4114567422942299</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1102176842995503</v>
+        <v>0.1121176842995503</v>
       </c>
       <c r="C21">
-        <v>142.199042572906</v>
+        <v>131.4855198680418</v>
       </c>
       <c r="D21">
-        <v>208.3440105960356</v>
+        <v>202.3749598923888</v>
       </c>
       <c r="E21">
-        <v>-108.802232098605</v>
+        <v>-104.0577600973876</v>
       </c>
       <c r="F21">
-        <v>90.14496802312956</v>
+        <v>94.88944002434692</v>
       </c>
       <c r="G21">
         <v>24</v>
@@ -2991,37 +2991,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M21">
-        <v>21.25618345985395</v>
+        <v>22.37492995774101</v>
       </c>
       <c r="N21">
-        <v>-12.51018345985395</v>
+        <v>-13.62892995774101</v>
       </c>
       <c r="O21">
-        <v>-3.099425426407735</v>
+        <v>-3.376597328193436</v>
       </c>
       <c r="P21">
-        <v>-9.410758033446218</v>
+        <v>-10.25233262954757</v>
       </c>
       <c r="Q21">
-        <v>-4.380758033446218</v>
+        <v>-5.22233262954757</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08639848065980058</v>
+        <v>0.08690596166804807</v>
       </c>
       <c r="T21">
-        <v>0.7455451991990004</v>
+        <v>0.7548645141889879</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.1019393115237751</v>
+        <v>0.09684234594758634</v>
       </c>
       <c r="W21">
-        <v>0.2117627103426938</v>
+        <v>0.2129645748255591</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.4114567422942299</v>
+        <v>0.3908839051795183</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1121176842995503</v>
+        <v>0.1140176842995503</v>
       </c>
       <c r="C22">
-        <v>131.4855198680418</v>
+        <v>121.1044973485291</v>
       </c>
       <c r="D22">
-        <v>202.3749598923888</v>
+        <v>196.7384093740933</v>
       </c>
       <c r="E22">
-        <v>-104.0577600973876</v>
+        <v>-99.3132880961703</v>
       </c>
       <c r="F22">
-        <v>94.88944002434692</v>
+        <v>99.63391202556427</v>
       </c>
       <c r="G22">
         <v>24</v>
@@ -3073,37 +3073,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M22">
-        <v>22.37492995774101</v>
+        <v>23.49367645562806</v>
       </c>
       <c r="N22">
-        <v>-13.62892995774101</v>
+        <v>-14.74767645562806</v>
       </c>
       <c r="O22">
-        <v>-3.376597328193436</v>
+        <v>-3.653769229979136</v>
       </c>
       <c r="P22">
-        <v>-10.25233262954757</v>
+        <v>-11.09390722564892</v>
       </c>
       <c r="Q22">
-        <v>-5.22233262954757</v>
+        <v>-6.063907225648919</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08690596166804807</v>
+        <v>0.08742629029675755</v>
       </c>
       <c r="T22">
-        <v>0.7548645141889879</v>
+        <v>0.7644197612040384</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.09684234594758634</v>
+        <v>0.09223080566436795</v>
       </c>
       <c r="W22">
-        <v>0.2129645748255591</v>
+        <v>0.2140519760243421</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3908839051795183</v>
+        <v>0.3722703858852555</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1140176842995503</v>
+        <v>0.1159176842995503</v>
       </c>
       <c r="C23">
-        <v>121.1044973485292</v>
+        <v>111.0289454415087</v>
       </c>
       <c r="D23">
-        <v>196.7384093740934</v>
+        <v>191.4073294682903</v>
       </c>
       <c r="E23">
-        <v>-99.31328809617031</v>
+        <v>-94.56881609495296</v>
       </c>
       <c r="F23">
-        <v>99.63391202556426</v>
+        <v>104.3783840267816</v>
       </c>
       <c r="G23">
         <v>24</v>
@@ -3155,37 +3155,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M23">
-        <v>23.49367645562805</v>
+        <v>24.6124229535151</v>
       </c>
       <c r="N23">
-        <v>-14.74767645562805</v>
+        <v>-15.86642295351511</v>
       </c>
       <c r="O23">
-        <v>-3.653769229979135</v>
+        <v>-3.930941131764836</v>
       </c>
       <c r="P23">
-        <v>-11.09390722564892</v>
+        <v>-11.93548182175027</v>
       </c>
       <c r="Q23">
-        <v>-6.063907225648918</v>
+        <v>-6.905481821750269</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08742629029675755</v>
+        <v>0.08795996068517752</v>
       </c>
       <c r="T23">
-        <v>0.7644197612040384</v>
+        <v>0.7742200145528082</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.09223080566436796</v>
+        <v>0.0880384963159876</v>
       </c>
       <c r="W23">
-        <v>0.2140519760243421</v>
+        <v>0.2150405225686901</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3722703858852556</v>
+        <v>0.355349004708653</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1159176842995503</v>
+        <v>0.1178176842995503</v>
       </c>
       <c r="C24">
-        <v>111.0289454415087</v>
+        <v>101.2346869951026</v>
       </c>
       <c r="D24">
-        <v>191.4073294682903</v>
+        <v>186.3575430231016</v>
       </c>
       <c r="E24">
-        <v>-94.56881609495296</v>
+        <v>-89.82434409373562</v>
       </c>
       <c r="F24">
-        <v>104.3783840267816</v>
+        <v>109.1228560279989</v>
       </c>
       <c r="G24">
         <v>24</v>
@@ -3237,37 +3237,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M24">
-        <v>24.6124229535151</v>
+        <v>25.73116945140215</v>
       </c>
       <c r="N24">
-        <v>-15.86642295351511</v>
+        <v>-16.98516945140215</v>
       </c>
       <c r="O24">
-        <v>-3.930941131764836</v>
+        <v>-4.208113033550536</v>
       </c>
       <c r="P24">
-        <v>-11.93548182175027</v>
+        <v>-12.77705641785162</v>
       </c>
       <c r="Q24">
-        <v>-6.905481821750269</v>
+        <v>-7.747056417851618</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08795996068517752</v>
+        <v>0.08850749264212787</v>
       </c>
       <c r="T24">
-        <v>0.7742200145528082</v>
+        <v>0.7842748199366109</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.0880384963159876</v>
+        <v>0.08421073560659684</v>
       </c>
       <c r="W24">
-        <v>0.2150405225686901</v>
+        <v>0.2159431085439645</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.355349004708653</v>
+        <v>0.3398990479821898</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1178176842995503</v>
+        <v>0.1197176842995503</v>
       </c>
       <c r="C25">
-        <v>101.2346869951026</v>
+        <v>91.70003068144121</v>
       </c>
       <c r="D25">
-        <v>186.3575430231016</v>
+        <v>181.5673587106575</v>
       </c>
       <c r="E25">
-        <v>-89.82434409373562</v>
+        <v>-85.07987209251826</v>
       </c>
       <c r="F25">
-        <v>109.1228560279989</v>
+        <v>113.8673280292163</v>
       </c>
       <c r="G25">
         <v>24</v>
@@ -3319,37 +3319,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M25">
-        <v>25.73116945140215</v>
+        <v>26.84991594928921</v>
       </c>
       <c r="N25">
-        <v>-16.98516945140215</v>
+        <v>-18.10391594928921</v>
       </c>
       <c r="O25">
-        <v>-4.208113033550536</v>
+        <v>-4.485284935336238</v>
       </c>
       <c r="P25">
-        <v>-12.77705641785162</v>
+        <v>-13.61863101395297</v>
       </c>
       <c r="Q25">
-        <v>-7.747056417851618</v>
+        <v>-8.58863101395297</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08850749264212787</v>
+        <v>0.08906943333478745</v>
       </c>
       <c r="T25">
-        <v>0.7842748199366109</v>
+        <v>0.7945942254620926</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.08421073560659684</v>
+        <v>0.08070195495632196</v>
       </c>
       <c r="W25">
-        <v>0.2159431085439645</v>
+        <v>0.2167704790212993</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3398990479821898</v>
+        <v>0.3257365876495986</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1197176842995503</v>
+        <v>0.1216176842995503</v>
       </c>
       <c r="C26">
-        <v>91.70003068144122</v>
+        <v>82.40545952146738</v>
       </c>
       <c r="D26">
-        <v>181.5673587106575</v>
+        <v>177.017259551901</v>
       </c>
       <c r="E26">
-        <v>-85.07987209251827</v>
+        <v>-80.33540009130093</v>
       </c>
       <c r="F26">
-        <v>113.8673280292163</v>
+        <v>118.6118000304336</v>
       </c>
       <c r="G26">
         <v>24</v>
@@ -3401,37 +3401,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M26">
-        <v>26.8499159492892</v>
+        <v>27.96866244717625</v>
       </c>
       <c r="N26">
-        <v>-18.10391594928921</v>
+        <v>-19.22266244717625</v>
       </c>
       <c r="O26">
-        <v>-4.485284935336237</v>
+        <v>-4.762456837121936</v>
       </c>
       <c r="P26">
-        <v>-13.61863101395297</v>
+        <v>-14.46020561005432</v>
       </c>
       <c r="Q26">
-        <v>-8.58863101395297</v>
+        <v>-9.430205610054319</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08906943333478745</v>
+        <v>0.08964635911258462</v>
       </c>
       <c r="T26">
-        <v>0.7945942254620926</v>
+        <v>0.8051888151349206</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.08070195495632197</v>
+        <v>0.07747387675806909</v>
       </c>
       <c r="W26">
-        <v>0.2167704790212993</v>
+        <v>0.2175316598604473</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3257365876495986</v>
+        <v>0.3127071241436147</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1216176842995503</v>
+        <v>0.1235176842995503</v>
       </c>
       <c r="C27">
-        <v>82.40545952146738</v>
+        <v>73.33336509840494</v>
       </c>
       <c r="D27">
-        <v>177.017259551901</v>
+        <v>172.6896371300559</v>
       </c>
       <c r="E27">
-        <v>-80.33540009130093</v>
+        <v>-75.59092809008358</v>
       </c>
       <c r="F27">
-        <v>118.6118000304336</v>
+        <v>123.356272031651</v>
       </c>
       <c r="G27">
         <v>24</v>
@@ -3483,37 +3483,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M27">
-        <v>27.96866244717625</v>
+        <v>29.08740894506331</v>
       </c>
       <c r="N27">
-        <v>-19.22266244717625</v>
+        <v>-20.34140894506331</v>
       </c>
       <c r="O27">
-        <v>-4.762456837121936</v>
+        <v>-5.039628738907637</v>
       </c>
       <c r="P27">
-        <v>-14.46020561005432</v>
+        <v>-15.30178020615567</v>
       </c>
       <c r="Q27">
-        <v>-9.430205610054319</v>
+        <v>-10.27178020615567</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08964635911258462</v>
+        <v>0.09023887747897089</v>
       </c>
       <c r="T27">
-        <v>0.8051888151349206</v>
+        <v>0.8160697450691762</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.07747387675806909</v>
+        <v>0.07449411226737411</v>
       </c>
       <c r="W27">
-        <v>0.2175316598604473</v>
+        <v>0.2182342883273532</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.3127071241436147</v>
+        <v>0.300679927061168</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1235176842995503</v>
+        <v>0.1254176842995503</v>
       </c>
       <c r="C28">
-        <v>73.33336509840494</v>
+        <v>64.46781982767831</v>
       </c>
       <c r="D28">
-        <v>172.6896371300559</v>
+        <v>168.5685638605466</v>
       </c>
       <c r="E28">
-        <v>-75.59092809008358</v>
+        <v>-70.84645608886623</v>
       </c>
       <c r="F28">
-        <v>123.356272031651</v>
+        <v>128.1007440328683</v>
       </c>
       <c r="G28">
         <v>24</v>
@@ -3565,37 +3565,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M28">
-        <v>29.08740894506331</v>
+        <v>30.20615544295035</v>
       </c>
       <c r="N28">
-        <v>-20.34140894506331</v>
+        <v>-21.46015544295036</v>
       </c>
       <c r="O28">
-        <v>-5.039628738907637</v>
+        <v>-5.316800640693337</v>
       </c>
       <c r="P28">
-        <v>-15.30178020615567</v>
+        <v>-16.14335480225702</v>
       </c>
       <c r="Q28">
-        <v>-10.27178020615567</v>
+        <v>-11.11335480225702</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09023887747897089</v>
+        <v>0.09084762922525816</v>
       </c>
       <c r="T28">
-        <v>0.8160697450691762</v>
+        <v>0.8272487826728635</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.07449411226737411</v>
+        <v>0.0717350710722862</v>
       </c>
       <c r="W28">
-        <v>0.2182342883273532</v>
+        <v>0.2188848702411549</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.300679927061168</v>
+        <v>0.2895436334663098</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1254176842995503</v>
+        <v>0.1273176842995503</v>
       </c>
       <c r="C29">
-        <v>64.46781982767831</v>
+        <v>55.7943810741902</v>
       </c>
       <c r="D29">
-        <v>168.5685638605466</v>
+        <v>164.6395971082759</v>
       </c>
       <c r="E29">
-        <v>-70.84645608886623</v>
+        <v>-66.10198408764887</v>
       </c>
       <c r="F29">
-        <v>128.1007440328683</v>
+        <v>132.8452160340857</v>
       </c>
       <c r="G29">
         <v>24</v>
@@ -3647,37 +3647,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M29">
-        <v>30.20615544295035</v>
+        <v>31.32490194083741</v>
       </c>
       <c r="N29">
-        <v>-21.46015544295036</v>
+        <v>-22.57890194083741</v>
       </c>
       <c r="O29">
-        <v>-5.316800640693337</v>
+        <v>-5.593972542479038</v>
       </c>
       <c r="P29">
-        <v>-16.14335480225702</v>
+        <v>-16.98492939835837</v>
       </c>
       <c r="Q29">
-        <v>-11.11335480225702</v>
+        <v>-11.95492939835837</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09084762922525816</v>
+        <v>0.09147329074227564</v>
       </c>
       <c r="T29">
-        <v>0.8272487826728635</v>
+        <v>0.8387383490988755</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.0717350710722862</v>
+        <v>0.06917310424827597</v>
       </c>
       <c r="W29">
-        <v>0.2188848702411549</v>
+        <v>0.2194889820182565</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2895436334663098</v>
+        <v>0.2792027894139416</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1273176842995503</v>
+        <v>0.1292176842995503</v>
       </c>
       <c r="C30">
-        <v>55.7943810741902</v>
+        <v>47.29992203925926</v>
       </c>
       <c r="D30">
-        <v>164.6395971082759</v>
+        <v>160.8896100745623</v>
       </c>
       <c r="E30">
-        <v>-66.10198408764887</v>
+        <v>-61.35751208643151</v>
       </c>
       <c r="F30">
-        <v>132.8452160340857</v>
+        <v>137.5896880353031</v>
       </c>
       <c r="G30">
         <v>24</v>
@@ -3729,37 +3729,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M30">
-        <v>31.32490194083741</v>
+        <v>32.44364843872446</v>
       </c>
       <c r="N30">
-        <v>-22.57890194083741</v>
+        <v>-23.69764843872446</v>
       </c>
       <c r="O30">
-        <v>-5.593972542479038</v>
+        <v>-5.871144444264738</v>
       </c>
       <c r="P30">
-        <v>-16.98492939835837</v>
+        <v>-17.82650399445972</v>
       </c>
       <c r="Q30">
-        <v>-11.95492939835837</v>
+        <v>-12.79650399445972</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09147329074227564</v>
+        <v>0.09211657652737812</v>
       </c>
       <c r="T30">
-        <v>0.8387383490988755</v>
+        <v>0.8505515652833667</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.06917310424827597</v>
+        <v>0.06678782479143885</v>
       </c>
       <c r="W30">
-        <v>0.2194889820182565</v>
+        <v>0.2200514309141787</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2792027894139416</v>
+        <v>0.2695751070203575</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1292176842995503</v>
+        <v>0.1311176842995503</v>
       </c>
       <c r="C31">
-        <v>47.29992203925934</v>
+        <v>38.97248524415014</v>
       </c>
       <c r="D31">
-        <v>160.8896100745624</v>
+        <v>157.3066452806705</v>
       </c>
       <c r="E31">
-        <v>-61.35751208643154</v>
+        <v>-56.61304008521421</v>
       </c>
       <c r="F31">
-        <v>137.589688035303</v>
+        <v>142.3341600365204</v>
       </c>
       <c r="G31">
         <v>24</v>
@@ -3811,37 +3811,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M31">
-        <v>32.44364843872445</v>
+        <v>33.5623949366115</v>
       </c>
       <c r="N31">
-        <v>-23.69764843872445</v>
+        <v>-24.81639493661151</v>
       </c>
       <c r="O31">
-        <v>-5.871144444264737</v>
+        <v>-6.148316346050438</v>
       </c>
       <c r="P31">
-        <v>-17.82650399445972</v>
+        <v>-18.66807859056107</v>
       </c>
       <c r="Q31">
-        <v>-12.79650399445972</v>
+        <v>-13.63807859056107</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09211657652737812</v>
+        <v>0.09277824190634065</v>
       </c>
       <c r="T31">
-        <v>0.8505515652833667</v>
+        <v>0.8627023019302719</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.06678782479143887</v>
+        <v>0.06456156396505758</v>
       </c>
       <c r="W31">
-        <v>0.2200514309141787</v>
+        <v>0.2205763832170394</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2695751070203575</v>
+        <v>0.2605892701196789</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1311176842995503</v>
+        <v>0.1330176842995503</v>
       </c>
       <c r="C32">
-        <v>38.97248524415014</v>
+        <v>30.80115516439494</v>
       </c>
       <c r="D32">
-        <v>157.3066452806705</v>
+        <v>153.8797872021327</v>
       </c>
       <c r="E32">
-        <v>-56.61304008521421</v>
+        <v>-51.86856808399685</v>
       </c>
       <c r="F32">
-        <v>142.3341600365204</v>
+        <v>147.0786320377377</v>
       </c>
       <c r="G32">
         <v>24</v>
@@ -3893,37 +3893,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M32">
-        <v>33.5623949366115</v>
+        <v>34.68114143449856</v>
       </c>
       <c r="N32">
-        <v>-24.81639493661151</v>
+        <v>-25.93514143449856</v>
       </c>
       <c r="O32">
-        <v>-6.148316346050438</v>
+        <v>-6.425488247836138</v>
       </c>
       <c r="P32">
-        <v>-18.66807859056107</v>
+        <v>-19.50965318666242</v>
       </c>
       <c r="Q32">
-        <v>-13.63807859056107</v>
+        <v>-14.47965318666242</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09277824190634065</v>
+        <v>0.09345908599193981</v>
       </c>
       <c r="T32">
-        <v>0.8627023019302719</v>
+        <v>0.875205233842305</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.06456156396505758</v>
+        <v>0.06247893286941054</v>
       </c>
       <c r="W32">
-        <v>0.2205763832170394</v>
+        <v>0.221067467629393</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2605892701196789</v>
+        <v>0.2521831646319473</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1330176842995503</v>
+        <v>0.1349176842995503</v>
       </c>
       <c r="C33">
-        <v>30.80115516439494</v>
+        <v>22.77594715682775</v>
       </c>
       <c r="D33">
-        <v>153.8797872021327</v>
+        <v>150.5990511957828</v>
       </c>
       <c r="E33">
-        <v>-51.86856808399685</v>
+        <v>-47.12409608277952</v>
       </c>
       <c r="F33">
-        <v>147.0786320377377</v>
+        <v>151.8231040389551</v>
       </c>
       <c r="G33">
         <v>24</v>
@@ -3975,37 +3975,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M33">
-        <v>34.68114143449856</v>
+        <v>35.7998879323856</v>
       </c>
       <c r="N33">
-        <v>-25.93514143449856</v>
+        <v>-27.0538879323856</v>
       </c>
       <c r="O33">
-        <v>-6.425488247836138</v>
+        <v>-6.702660149621837</v>
       </c>
       <c r="P33">
-        <v>-19.50965318666242</v>
+        <v>-20.35122778276376</v>
       </c>
       <c r="Q33">
-        <v>-14.47965318666242</v>
+        <v>-15.32122778276376</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09345908599193981</v>
+        <v>0.09415995490358597</v>
       </c>
       <c r="T33">
-        <v>0.875205233842305</v>
+        <v>0.8880758990458683</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.06247893286941054</v>
+        <v>0.06052646621724148</v>
       </c>
       <c r="W33">
-        <v>0.221067467629393</v>
+        <v>0.2215278592659745</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2521831646319473</v>
+        <v>0.244302440737199</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1349176842995503</v>
+        <v>0.1368176842995503</v>
       </c>
       <c r="C34">
-        <v>22.77594715682775</v>
+        <v>14.88771029854954</v>
       </c>
       <c r="D34">
-        <v>150.5990511957828</v>
+        <v>147.4552863387219</v>
       </c>
       <c r="E34">
-        <v>-47.12409608277952</v>
+        <v>-42.37962408156216</v>
       </c>
       <c r="F34">
-        <v>151.8231040389551</v>
+        <v>156.5675760401724</v>
       </c>
       <c r="G34">
         <v>24</v>
@@ -4057,37 +4057,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M34">
-        <v>35.7998879323856</v>
+        <v>36.91863443027265</v>
       </c>
       <c r="N34">
-        <v>-27.0538879323856</v>
+        <v>-28.17263443027266</v>
       </c>
       <c r="O34">
-        <v>-6.702660149621837</v>
+        <v>-6.979832051407538</v>
       </c>
       <c r="P34">
-        <v>-20.35122778276376</v>
+        <v>-21.19280237886512</v>
       </c>
       <c r="Q34">
-        <v>-15.32122778276376</v>
+        <v>-16.16280237886512</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09415995490358597</v>
+        <v>0.09488174527528129</v>
       </c>
       <c r="T34">
-        <v>0.8880758990458683</v>
+        <v>0.9013307632107319</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.06052646621724148</v>
+        <v>0.05869233087732507</v>
       </c>
       <c r="W34">
-        <v>0.2215278592659745</v>
+        <v>0.2219603483791268</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.244302440737199</v>
+        <v>0.2368993364724353</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1368176842995503</v>
+        <v>0.1387176842995503</v>
       </c>
       <c r="C35">
-        <v>14.88771029854954</v>
+        <v>7.128042146507255</v>
       </c>
       <c r="D35">
-        <v>147.4552863387219</v>
+        <v>144.440090187897</v>
       </c>
       <c r="E35">
-        <v>-42.37962408156216</v>
+        <v>-37.6351520803448</v>
       </c>
       <c r="F35">
-        <v>156.5675760401724</v>
+        <v>161.3120480413898</v>
       </c>
       <c r="G35">
         <v>24</v>
@@ -4139,37 +4139,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M35">
-        <v>36.91863443027265</v>
+        <v>38.03738092815971</v>
       </c>
       <c r="N35">
-        <v>-28.17263443027266</v>
+        <v>-29.29138092815971</v>
       </c>
       <c r="O35">
-        <v>-6.979832051407538</v>
+        <v>-7.25700395319324</v>
       </c>
       <c r="P35">
-        <v>-21.19280237886512</v>
+        <v>-22.03437697496647</v>
       </c>
       <c r="Q35">
-        <v>-16.16280237886512</v>
+        <v>-17.00437697496647</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09488174527528129</v>
+        <v>0.09562540808248252</v>
       </c>
       <c r="T35">
-        <v>0.9013307632107319</v>
+        <v>0.9149872899260461</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.05869233087732507</v>
+        <v>0.05696608585152138</v>
       </c>
       <c r="W35">
-        <v>0.2219603483791268</v>
+        <v>0.2223673969562113</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2368993364724353</v>
+        <v>0.2299317089291284</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1387176842995503</v>
+        <v>0.1406176842995503</v>
       </c>
       <c r="C36">
-        <v>7.128042146507255</v>
+        <v>-0.5107862544087141</v>
       </c>
       <c r="D36">
-        <v>144.440090187897</v>
+        <v>141.5457337881984</v>
       </c>
       <c r="E36">
-        <v>-37.6351520803448</v>
+        <v>-32.89068007912746</v>
       </c>
       <c r="F36">
-        <v>161.3120480413898</v>
+        <v>166.0565200426071</v>
       </c>
       <c r="G36">
         <v>24</v>
@@ -4221,37 +4221,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M36">
-        <v>38.03738092815971</v>
+        <v>39.15612742604676</v>
       </c>
       <c r="N36">
-        <v>-29.29138092815971</v>
+        <v>-30.41012742604676</v>
       </c>
       <c r="O36">
-        <v>-7.25700395319324</v>
+        <v>-7.534175854978939</v>
       </c>
       <c r="P36">
-        <v>-22.03437697496647</v>
+        <v>-22.87595157106782</v>
       </c>
       <c r="Q36">
-        <v>-17.00437697496647</v>
+        <v>-17.84595157106782</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09562540808248252</v>
+        <v>0.09639195282221302</v>
       </c>
       <c r="T36">
-        <v>0.9149872899260461</v>
+        <v>0.9290640174633699</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.05696608585152138</v>
+        <v>0.05533848339862077</v>
       </c>
       <c r="W36">
-        <v>0.2223673969562113</v>
+        <v>0.2227511856146052</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2299317089291284</v>
+        <v>0.2233622315311533</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1406176842995503</v>
+        <v>0.1425176842995503</v>
       </c>
       <c r="C37">
-        <v>-0.5107862544087141</v>
+        <v>-8.035896524059353</v>
       </c>
       <c r="D37">
-        <v>141.5457337881984</v>
+        <v>138.7650955197651</v>
       </c>
       <c r="E37">
-        <v>-32.89068007912746</v>
+        <v>-28.1462080779101</v>
       </c>
       <c r="F37">
-        <v>166.0565200426071</v>
+        <v>170.8009920438245</v>
       </c>
       <c r="G37">
         <v>24</v>
@@ -4303,37 +4303,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M37">
-        <v>39.15612742604676</v>
+        <v>40.27487392393381</v>
       </c>
       <c r="N37">
-        <v>-30.41012742604676</v>
+        <v>-31.52887392393381</v>
       </c>
       <c r="O37">
-        <v>-7.534175854978939</v>
+        <v>-7.81134775676464</v>
       </c>
       <c r="P37">
-        <v>-22.87595157106782</v>
+        <v>-23.71752616716917</v>
       </c>
       <c r="Q37">
-        <v>-17.84595157106782</v>
+        <v>-18.68752616716917</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09639195282221302</v>
+        <v>0.0971824520850601</v>
       </c>
       <c r="T37">
-        <v>0.9290640174633699</v>
+        <v>0.9435806427362351</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.05533848339862077</v>
+        <v>0.05380130330421463</v>
       </c>
       <c r="W37">
-        <v>0.2227511856146052</v>
+        <v>0.2231136526808662</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2233622315311533</v>
+        <v>0.2171577250997324</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1425176842995503</v>
+        <v>0.1444176842995503</v>
       </c>
       <c r="C38">
-        <v>-8.035896524059325</v>
+        <v>-15.45386145263748</v>
       </c>
       <c r="D38">
-        <v>138.7650955197651</v>
+        <v>136.0916025924043</v>
       </c>
       <c r="E38">
-        <v>-28.14620807791013</v>
+        <v>-23.40173607669277</v>
       </c>
       <c r="F38">
-        <v>170.8009920438244</v>
+        <v>175.5454640450418</v>
       </c>
       <c r="G38">
         <v>24</v>
@@ -4385,37 +4385,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M38">
-        <v>40.2748739239338</v>
+        <v>41.39362042182086</v>
       </c>
       <c r="N38">
-        <v>-31.5288739239338</v>
+        <v>-32.64762042182086</v>
       </c>
       <c r="O38">
-        <v>-7.811347756764638</v>
+        <v>-8.088519658550339</v>
       </c>
       <c r="P38">
-        <v>-23.71752616716917</v>
+        <v>-24.55910076327052</v>
       </c>
       <c r="Q38">
-        <v>-18.68752616716917</v>
+        <v>-19.52910076327052</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.0971824520850601</v>
+        <v>0.09799804656260074</v>
       </c>
       <c r="T38">
-        <v>0.9435806427362349</v>
+        <v>0.9585581132558578</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.05380130330421464</v>
+        <v>0.05234721402572235</v>
       </c>
       <c r="W38">
-        <v>0.2231136526808662</v>
+        <v>0.2234565269327347</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2171577250997324</v>
+        <v>0.2112885973943341</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1444176842995503</v>
+        <v>0.1463176842995503</v>
       </c>
       <c r="C39">
-        <v>-15.45386145263748</v>
+        <v>-22.77075687096217</v>
       </c>
       <c r="D39">
-        <v>136.0916025924043</v>
+        <v>133.519179175297</v>
       </c>
       <c r="E39">
-        <v>-23.40173607669277</v>
+        <v>-18.65726407547544</v>
       </c>
       <c r="F39">
-        <v>175.5454640450418</v>
+        <v>180.2899360462591</v>
       </c>
       <c r="G39">
         <v>24</v>
@@ -4467,37 +4467,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M39">
-        <v>41.39362042182086</v>
+        <v>42.5123669197079</v>
       </c>
       <c r="N39">
-        <v>-32.64762042182086</v>
+        <v>-33.76636691970791</v>
       </c>
       <c r="O39">
-        <v>-8.088519658550339</v>
+        <v>-8.365691560336039</v>
       </c>
       <c r="P39">
-        <v>-24.55910076327052</v>
+        <v>-25.40067535937187</v>
       </c>
       <c r="Q39">
-        <v>-19.52910076327052</v>
+        <v>-20.37067535937187</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09799804656260074</v>
+        <v>0.09883995053941687</v>
       </c>
       <c r="T39">
-        <v>0.9585581132558578</v>
+        <v>0.9740187279857908</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.05234721402572235</v>
+        <v>0.05096965576188756</v>
       </c>
       <c r="W39">
-        <v>0.2234565269327347</v>
+        <v>0.2237813551713469</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2112885973943341</v>
+        <v>0.2057283711471148</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1463176842995503</v>
+        <v>0.1482176842995503</v>
       </c>
       <c r="C40">
-        <v>-22.77075687096217</v>
+        <v>-29.99220774714692</v>
       </c>
       <c r="D40">
-        <v>133.519179175297</v>
+        <v>131.0422003003296</v>
       </c>
       <c r="E40">
-        <v>-18.65726407547544</v>
+        <v>-13.91279207425808</v>
       </c>
       <c r="F40">
-        <v>180.2899360462591</v>
+        <v>185.0344080474765</v>
       </c>
       <c r="G40">
         <v>24</v>
@@ -4549,37 +4549,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M40">
-        <v>42.5123669197079</v>
+        <v>43.63111341759496</v>
       </c>
       <c r="N40">
-        <v>-33.76636691970791</v>
+        <v>-34.88511341759497</v>
       </c>
       <c r="O40">
-        <v>-8.365691560336039</v>
+        <v>-8.642863462121742</v>
       </c>
       <c r="P40">
-        <v>-25.40067535937187</v>
+        <v>-26.24224995547322</v>
       </c>
       <c r="Q40">
-        <v>-20.37067535937187</v>
+        <v>-21.21224995547322</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09883995053941687</v>
+        <v>0.09970945792530896</v>
       </c>
       <c r="T40">
-        <v>0.9740187279857908</v>
+        <v>0.9899862481167055</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.05096965576188756</v>
+        <v>0.04966274151158274</v>
       </c>
       <c r="W40">
-        <v>0.2237813551713469</v>
+        <v>0.2240895255515688</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2057283711471148</v>
+        <v>0.2004532847074452</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1482176842995503</v>
+        <v>0.1501176842995503</v>
       </c>
       <c r="C41">
-        <v>-29.99220774714692</v>
+        <v>-37.12342924575225</v>
       </c>
       <c r="D41">
-        <v>131.0422003003296</v>
+        <v>128.6554508029416</v>
       </c>
       <c r="E41">
-        <v>-13.91279207425808</v>
+        <v>-9.168320073040718</v>
       </c>
       <c r="F41">
-        <v>185.0344080474765</v>
+        <v>189.7788800486938</v>
       </c>
       <c r="G41">
         <v>24</v>
@@ -4631,37 +4631,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M41">
-        <v>43.63111341759496</v>
+        <v>44.74985991548201</v>
       </c>
       <c r="N41">
-        <v>-34.88511341759497</v>
+        <v>-36.00385991548201</v>
       </c>
       <c r="O41">
-        <v>-8.642863462121742</v>
+        <v>-8.92003536390744</v>
       </c>
       <c r="P41">
-        <v>-26.24224995547322</v>
+        <v>-27.08382455157457</v>
       </c>
       <c r="Q41">
-        <v>-21.21224995547322</v>
+        <v>-22.05382455157457</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09970945792530896</v>
+        <v>0.1006079488907308</v>
       </c>
       <c r="T41">
-        <v>0.9899862481167055</v>
+        <v>1.006486018918651</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.04966274151158274</v>
+        <v>0.04842117297379317</v>
       </c>
       <c r="W41">
-        <v>0.2240895255515688</v>
+        <v>0.2243822874127796</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2004532847074452</v>
+        <v>0.1954419525897593</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1501176842995503</v>
+        <v>0.1520176842995503</v>
       </c>
       <c r="C42">
-        <v>-37.12342924575225</v>
+        <v>-44.16926338019232</v>
       </c>
       <c r="D42">
-        <v>128.6554508029416</v>
+        <v>126.3540886697189</v>
       </c>
       <c r="E42">
-        <v>-9.168320073040718</v>
+        <v>-4.423848071823386</v>
       </c>
       <c r="F42">
-        <v>189.7788800486938</v>
+        <v>194.5233520499112</v>
       </c>
       <c r="G42">
         <v>24</v>
@@ -4713,37 +4713,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M42">
-        <v>44.74985991548201</v>
+        <v>45.86860641336906</v>
       </c>
       <c r="N42">
-        <v>-36.00385991548201</v>
+        <v>-37.12260641336906</v>
       </c>
       <c r="O42">
-        <v>-8.92003536390744</v>
+        <v>-9.197207265693139</v>
       </c>
       <c r="P42">
-        <v>-27.08382455157457</v>
+        <v>-27.92539914767592</v>
       </c>
       <c r="Q42">
-        <v>-22.05382455157457</v>
+        <v>-22.89539914767592</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1006079488907308</v>
+        <v>0.1015368971770143</v>
       </c>
       <c r="T42">
-        <v>1.006486018918651</v>
+        <v>1.023545103985068</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.04842117297379317</v>
+        <v>0.04724016875492017</v>
       </c>
       <c r="W42">
-        <v>0.2243822874127796</v>
+        <v>0.2246607682075898</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1954419525897593</v>
+        <v>0.1906750756973261</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1520176842995503</v>
+        <v>0.1539176842995503</v>
       </c>
       <c r="C43">
-        <v>-44.16926338019232</v>
+        <v>-51.13421180048763</v>
       </c>
       <c r="D43">
-        <v>126.3540886697189</v>
+        <v>124.1336122506409</v>
       </c>
       <c r="E43">
-        <v>-4.423848071823386</v>
+        <v>0.3206239293939745</v>
       </c>
       <c r="F43">
-        <v>194.5233520499112</v>
+        <v>199.2678240511285</v>
       </c>
       <c r="G43">
         <v>24</v>
@@ -4795,37 +4795,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M43">
-        <v>45.86860641336906</v>
+        <v>46.98735291125611</v>
       </c>
       <c r="N43">
-        <v>-37.12260641336906</v>
+        <v>-38.24135291125612</v>
       </c>
       <c r="O43">
-        <v>-9.197207265693139</v>
+        <v>-9.474379167478842</v>
       </c>
       <c r="P43">
-        <v>-27.92539914767592</v>
+        <v>-28.76697374377727</v>
       </c>
       <c r="Q43">
-        <v>-22.89539914767592</v>
+        <v>-23.73697374377727</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1015368971770143</v>
+        <v>0.1024978781628249</v>
       </c>
       <c r="T43">
-        <v>1.023545103985068</v>
+        <v>1.041192433364121</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.04724016875492017</v>
+        <v>0.04611540283218397</v>
       </c>
       <c r="W43">
-        <v>0.2246607682075898</v>
+        <v>0.224925988012171</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1906750756973261</v>
+        <v>0.1861351929426277</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1539176842995503</v>
+        <v>0.1558176842995503</v>
       </c>
       <c r="C44">
-        <v>-51.13421180048761</v>
+        <v>-58.02246518356031</v>
       </c>
       <c r="D44">
-        <v>124.1336122506409</v>
+        <v>121.9898308687856</v>
       </c>
       <c r="E44">
-        <v>0.3206239293939461</v>
+        <v>5.065095930611307</v>
       </c>
       <c r="F44">
-        <v>199.2678240511285</v>
+        <v>204.0122960523459</v>
       </c>
       <c r="G44">
         <v>24</v>
@@ -4877,37 +4877,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M44">
-        <v>46.9873529112561</v>
+        <v>48.10609940914316</v>
       </c>
       <c r="N44">
-        <v>-38.2413529112561</v>
+        <v>-39.36009940914316</v>
       </c>
       <c r="O44">
-        <v>-9.474379167478839</v>
+        <v>-9.75155106926454</v>
       </c>
       <c r="P44">
-        <v>-28.76697374377726</v>
+        <v>-29.60854833987862</v>
       </c>
       <c r="Q44">
-        <v>-23.73697374377726</v>
+        <v>-24.57854833987862</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1024978781628249</v>
+        <v>0.1034925777797166</v>
       </c>
       <c r="T44">
-        <v>1.041192433364121</v>
+        <v>1.05945896728279</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.04611540283218398</v>
+        <v>0.04504295160352853</v>
       </c>
       <c r="W44">
-        <v>0.224925988012171</v>
+        <v>0.225178872011888</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1861351929426279</v>
+        <v>0.1818064675253575</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1558176842995503</v>
+        <v>0.1577176842995503</v>
       </c>
       <c r="C45">
-        <v>-58.02246518356031</v>
+        <v>-64.83792962981718</v>
       </c>
       <c r="D45">
-        <v>121.9898308687856</v>
+        <v>119.918838423746</v>
       </c>
       <c r="E45">
-        <v>5.065095930611307</v>
+        <v>9.809567931828639</v>
       </c>
       <c r="F45">
-        <v>204.0122960523459</v>
+        <v>208.7567680535632</v>
       </c>
       <c r="G45">
         <v>24</v>
@@ -4959,37 +4959,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M45">
-        <v>48.10609940914316</v>
+        <v>49.22484590703021</v>
       </c>
       <c r="N45">
-        <v>-39.36009940914316</v>
+        <v>-40.47884590703021</v>
       </c>
       <c r="O45">
-        <v>-9.75155106926454</v>
+        <v>-10.02872297105024</v>
       </c>
       <c r="P45">
-        <v>-29.60854833987862</v>
+        <v>-30.45012293597997</v>
       </c>
       <c r="Q45">
-        <v>-24.57854833987862</v>
+        <v>-25.42012293597996</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1034925777797166</v>
+        <v>0.1045228023829258</v>
       </c>
       <c r="T45">
-        <v>1.05945896728279</v>
+        <v>1.07837787741284</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04504295160352853</v>
+        <v>0.0440192481579938</v>
       </c>
       <c r="W45">
-        <v>0.225178872011888</v>
+        <v>0.2254202612843451</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1818064675253575</v>
+        <v>0.1776745023543266</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1577176842995503</v>
+        <v>0.1596176842995503</v>
       </c>
       <c r="C46">
-        <v>-64.83792962981718</v>
+        <v>-71.5842504158461</v>
       </c>
       <c r="D46">
-        <v>119.918838423746</v>
+        <v>117.9169896389345</v>
       </c>
       <c r="E46">
-        <v>9.809567931828639</v>
+        <v>14.554039933046</v>
       </c>
       <c r="F46">
-        <v>208.7567680535632</v>
+        <v>213.5012400547806</v>
       </c>
       <c r="G46">
         <v>24</v>
@@ -5041,37 +5041,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M46">
-        <v>49.22484590703021</v>
+        <v>50.34359240491726</v>
       </c>
       <c r="N46">
-        <v>-40.47884590703021</v>
+        <v>-41.59759240491726</v>
       </c>
       <c r="O46">
-        <v>-10.02872297105024</v>
+        <v>-10.30589487283594</v>
       </c>
       <c r="P46">
-        <v>-30.45012293597997</v>
+        <v>-31.29169753208132</v>
       </c>
       <c r="Q46">
-        <v>-25.42012293597996</v>
+        <v>-26.26169753208132</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1045228023829258</v>
+        <v>0.105590489698979</v>
       </c>
       <c r="T46">
-        <v>1.07837787741284</v>
+        <v>1.097984747911255</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.0440192481579938</v>
+        <v>0.04304104264337171</v>
       </c>
       <c r="W46">
-        <v>0.2254202612843451</v>
+        <v>0.225650922144693</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1776745023543266</v>
+        <v>0.1737261800797858</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1596176842995503</v>
+        <v>0.1615176842995503</v>
       </c>
       <c r="C47">
-        <v>-71.5842504158461</v>
+        <v>-78.2648334071003</v>
       </c>
       <c r="D47">
-        <v>117.9169896389345</v>
+        <v>115.9808786488976</v>
       </c>
       <c r="E47">
-        <v>14.554039933046</v>
+        <v>19.29851193426333</v>
       </c>
       <c r="F47">
-        <v>213.5012400547806</v>
+        <v>218.2457120559979</v>
       </c>
       <c r="G47">
         <v>24</v>
@@ -5123,37 +5123,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M47">
-        <v>50.34359240491726</v>
+        <v>51.46233890280431</v>
       </c>
       <c r="N47">
-        <v>-41.59759240491726</v>
+        <v>-42.71633890280431</v>
       </c>
       <c r="O47">
-        <v>-10.30589487283594</v>
+        <v>-10.58306677462164</v>
       </c>
       <c r="P47">
-        <v>-31.29169753208132</v>
+        <v>-32.13327212818267</v>
       </c>
       <c r="Q47">
-        <v>-26.26169753208132</v>
+        <v>-27.10327212818267</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.105590489698979</v>
+        <v>0.1066977209897008</v>
       </c>
       <c r="T47">
-        <v>1.097984747911255</v>
+        <v>1.118317798798501</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04304104264337171</v>
+        <v>0.04210536780329842</v>
       </c>
       <c r="W47">
-        <v>0.225650922144693</v>
+        <v>0.2258715542719822</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1737261800797858</v>
+        <v>0.1699495239910949</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1615176842995503</v>
+        <v>0.1634176842995503</v>
       </c>
       <c r="C48">
-        <v>-78.2648334071003</v>
+        <v>-84.88286439517617</v>
       </c>
       <c r="D48">
-        <v>115.9808786488976</v>
+        <v>114.1073196620391</v>
       </c>
       <c r="E48">
-        <v>19.29851193426333</v>
+        <v>24.04298393548069</v>
       </c>
       <c r="F48">
-        <v>218.2457120559979</v>
+        <v>222.9901840572153</v>
       </c>
       <c r="G48">
         <v>24</v>
@@ -5205,37 +5205,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M48">
-        <v>51.46233890280431</v>
+        <v>52.58108540069136</v>
       </c>
       <c r="N48">
-        <v>-42.71633890280431</v>
+        <v>-43.83508540069136</v>
       </c>
       <c r="O48">
-        <v>-10.58306677462164</v>
+        <v>-10.86023867640734</v>
       </c>
       <c r="P48">
-        <v>-32.13327212818267</v>
+        <v>-32.97484672428401</v>
       </c>
       <c r="Q48">
-        <v>-27.10327212818267</v>
+        <v>-27.94484672428401</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1066977209897008</v>
+        <v>0.1078467345932801</v>
       </c>
       <c r="T48">
-        <v>1.118317798798501</v>
+        <v>1.139418134624888</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04210536780329842</v>
+        <v>0.04120950891386654</v>
       </c>
       <c r="W48">
-        <v>0.2258715542719822</v>
+        <v>0.2260827977981103</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1699495239910949</v>
+        <v>0.1663335766721356</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1634176842995503</v>
+        <v>0.1653176842995503</v>
       </c>
       <c r="C49">
-        <v>-84.88286439517617</v>
+        <v>-91.44132659063533</v>
       </c>
       <c r="D49">
-        <v>114.1073196620391</v>
+        <v>112.2933294677973</v>
       </c>
       <c r="E49">
-        <v>24.04298393548069</v>
+        <v>28.78745593669805</v>
       </c>
       <c r="F49">
-        <v>222.9901840572153</v>
+        <v>227.7346560584326</v>
       </c>
       <c r="G49">
         <v>24</v>
@@ -5287,37 +5287,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M49">
-        <v>52.58108540069136</v>
+        <v>53.69983189857842</v>
       </c>
       <c r="N49">
-        <v>-43.83508540069136</v>
+        <v>-44.95383189857841</v>
       </c>
       <c r="O49">
-        <v>-10.86023867640734</v>
+        <v>-11.13741057819304</v>
       </c>
       <c r="P49">
-        <v>-32.97484672428401</v>
+        <v>-33.81642132038537</v>
       </c>
       <c r="Q49">
-        <v>-27.94484672428401</v>
+        <v>-28.78642132038537</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1078467345932801</v>
+        <v>0.1090399410277663</v>
       </c>
       <c r="T49">
-        <v>1.139418134624888</v>
+        <v>1.161330021829212</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.04120950891386654</v>
+        <v>0.04035097747816098</v>
       </c>
       <c r="W49">
-        <v>0.2260827977981103</v>
+        <v>0.2262852395106497</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1663335766721356</v>
+        <v>0.1628682938247994</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1653176842995503</v>
+        <v>0.1672176842995503</v>
       </c>
       <c r="C50">
-        <v>-91.4413265906353</v>
+        <v>-97.94301647341294</v>
       </c>
       <c r="D50">
-        <v>112.2933294677973</v>
+        <v>110.536111586237</v>
       </c>
       <c r="E50">
-        <v>28.78745593669802</v>
+        <v>33.53192793791536</v>
       </c>
       <c r="F50">
-        <v>227.7346560584326</v>
+        <v>232.4791280596499</v>
       </c>
       <c r="G50">
         <v>24</v>
@@ -5369,37 +5369,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M50">
-        <v>53.69983189857841</v>
+        <v>54.81857839646545</v>
       </c>
       <c r="N50">
-        <v>-44.95383189857841</v>
+        <v>-46.07257839646546</v>
       </c>
       <c r="O50">
-        <v>-11.13741057819304</v>
+        <v>-11.41458247997874</v>
       </c>
       <c r="P50">
-        <v>-33.81642132038537</v>
+        <v>-34.65799591648672</v>
       </c>
       <c r="Q50">
-        <v>-28.78642132038537</v>
+        <v>-29.62799591648672</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1090399410277663</v>
+        <v>0.110279939871448</v>
       </c>
       <c r="T50">
-        <v>1.161330021829212</v>
+        <v>1.184101198727824</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.04035097747816099</v>
+        <v>0.03952748814187199</v>
       </c>
       <c r="W50">
-        <v>0.2262852395106497</v>
+        <v>0.2264794182961466</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1628682938247993</v>
+        <v>0.1595444510936809</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1672176842995503</v>
+        <v>0.1691176842995503</v>
       </c>
       <c r="C51">
-        <v>-97.94301647341294</v>
+        <v>-104.3905581779479</v>
       </c>
       <c r="D51">
-        <v>110.536111586237</v>
+        <v>108.8330418829193</v>
       </c>
       <c r="E51">
-        <v>33.53192793791536</v>
+        <v>38.27639993913272</v>
       </c>
       <c r="F51">
-        <v>232.4791280596499</v>
+        <v>237.2236000608673</v>
       </c>
       <c r="G51">
         <v>24</v>
@@ -5451,37 +5451,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M51">
-        <v>54.81857839646545</v>
+        <v>55.93732489435251</v>
       </c>
       <c r="N51">
-        <v>-46.07257839646546</v>
+        <v>-47.1913248943525</v>
       </c>
       <c r="O51">
-        <v>-11.41458247997874</v>
+        <v>-11.69175438176444</v>
       </c>
       <c r="P51">
-        <v>-34.65799591648672</v>
+        <v>-35.49957051258806</v>
       </c>
       <c r="Q51">
-        <v>-29.62799591648672</v>
+        <v>-30.46957051258806</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.110279939871448</v>
+        <v>0.1115695386688769</v>
       </c>
       <c r="T51">
-        <v>1.184101198727824</v>
+        <v>1.207783222702381</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.03952748814187199</v>
+        <v>0.03873693837903455</v>
       </c>
       <c r="W51">
-        <v>0.2264794182961466</v>
+        <v>0.2266658299302237</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1595444510936809</v>
+        <v>0.1563535620718074</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1691176842995503</v>
+        <v>0.1710176842995503</v>
       </c>
       <c r="C52">
-        <v>-104.3905581779479</v>
+        <v>-110.7864165686697</v>
       </c>
       <c r="D52">
-        <v>108.8330418829193</v>
+        <v>107.1816554934149</v>
       </c>
       <c r="E52">
-        <v>38.27639993913272</v>
+        <v>43.02087194035008</v>
       </c>
       <c r="F52">
-        <v>237.2236000608673</v>
+        <v>241.9680720620846</v>
       </c>
       <c r="G52">
         <v>24</v>
@@ -5533,37 +5533,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M52">
-        <v>55.93732489435251</v>
+        <v>57.05607139223956</v>
       </c>
       <c r="N52">
-        <v>-47.1913248943525</v>
+        <v>-48.31007139223956</v>
       </c>
       <c r="O52">
-        <v>-11.69175438176444</v>
+        <v>-11.96892628355014</v>
       </c>
       <c r="P52">
-        <v>-35.49957051258806</v>
+        <v>-36.34114510868942</v>
       </c>
       <c r="Q52">
-        <v>-30.46957051258806</v>
+        <v>-31.31114510868942</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1115695386688769</v>
+        <v>0.1129117741519152</v>
       </c>
       <c r="T52">
-        <v>1.207783222702381</v>
+        <v>1.232431859900389</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.03873693837903455</v>
+        <v>0.03797739056768092</v>
       </c>
       <c r="W52">
-        <v>0.2266658299302237</v>
+        <v>0.2268449313041409</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1563535620718074</v>
+        <v>0.1532878059527523</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1710176842995503</v>
+        <v>0.1729176842995503</v>
       </c>
       <c r="C53">
-        <v>-110.7864165686697</v>
+        <v>-117.1329091428674</v>
       </c>
       <c r="D53">
-        <v>107.1816554934149</v>
+        <v>105.5796349204346</v>
       </c>
       <c r="E53">
-        <v>43.02087194035008</v>
+        <v>47.76534394156741</v>
       </c>
       <c r="F53">
-        <v>241.9680720620846</v>
+        <v>246.712544063302</v>
       </c>
       <c r="G53">
         <v>24</v>
@@ -5615,37 +5615,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M53">
-        <v>57.05607139223956</v>
+        <v>58.17481789012661</v>
       </c>
       <c r="N53">
-        <v>-48.31007139223956</v>
+        <v>-49.42881789012661</v>
       </c>
       <c r="O53">
-        <v>-11.96892628355014</v>
+        <v>-12.24609818533584</v>
       </c>
       <c r="P53">
-        <v>-36.34114510868942</v>
+        <v>-37.18271970479077</v>
       </c>
       <c r="Q53">
-        <v>-31.31114510868942</v>
+        <v>-32.15271970479077</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1129117741519152</v>
+        <v>0.1143099361134134</v>
       </c>
       <c r="T53">
-        <v>1.232431859900389</v>
+        <v>1.258107523648313</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03797739056768092</v>
+        <v>0.03724705613368706</v>
       </c>
       <c r="W53">
-        <v>0.2268449313041409</v>
+        <v>0.2270171441636766</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1532878059527523</v>
+        <v>0.150339963530584</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1729176842995503</v>
+        <v>0.1748176842995503</v>
       </c>
       <c r="C54">
-        <v>-117.1329091428674</v>
+        <v>-123.4322168818202</v>
       </c>
       <c r="D54">
-        <v>105.5796349204346</v>
+        <v>104.0247991826991</v>
       </c>
       <c r="E54">
-        <v>47.76534394156741</v>
+        <v>52.50981594278477</v>
       </c>
       <c r="F54">
-        <v>246.712544063302</v>
+        <v>251.4570160645193</v>
       </c>
       <c r="G54">
         <v>24</v>
@@ -5697,37 +5697,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M54">
-        <v>58.17481789012661</v>
+        <v>59.29356438801366</v>
       </c>
       <c r="N54">
-        <v>-49.42881789012661</v>
+        <v>-50.54756438801367</v>
       </c>
       <c r="O54">
-        <v>-12.24609818533584</v>
+        <v>-12.52327008712154</v>
       </c>
       <c r="P54">
-        <v>-37.18271970479077</v>
+        <v>-38.02429430089212</v>
       </c>
       <c r="Q54">
-        <v>-32.15271970479077</v>
+        <v>-32.99429430089212</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1143099361134134</v>
+        <v>0.1157675943285925</v>
       </c>
       <c r="T54">
-        <v>1.258107523648313</v>
+        <v>1.28487576883232</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03724705613368706</v>
+        <v>0.03654428148965523</v>
       </c>
       <c r="W54">
-        <v>0.2270171441636766</v>
+        <v>0.2271828584247393</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.150339963530584</v>
+        <v>0.1475033604451012</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1748176842995503</v>
+        <v>0.1767176842995503</v>
       </c>
       <c r="C55">
-        <v>-123.4322168818202</v>
+        <v>-129.6863941570394</v>
       </c>
       <c r="D55">
-        <v>104.0247991826991</v>
+        <v>102.5150939086973</v>
       </c>
       <c r="E55">
-        <v>52.50981594278477</v>
+        <v>57.2542879440021</v>
       </c>
       <c r="F55">
-        <v>251.4570160645193</v>
+        <v>256.2014880657367</v>
       </c>
       <c r="G55">
         <v>24</v>
@@ -5779,37 +5779,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M55">
-        <v>59.29356438801366</v>
+        <v>60.41231088590071</v>
       </c>
       <c r="N55">
-        <v>-50.54756438801367</v>
+        <v>-51.66631088590071</v>
       </c>
       <c r="O55">
-        <v>-12.52327008712154</v>
+        <v>-12.80044198890724</v>
       </c>
       <c r="P55">
-        <v>-38.02429430089212</v>
+        <v>-38.86586889699347</v>
       </c>
       <c r="Q55">
-        <v>-32.99429430089212</v>
+        <v>-33.83586889699347</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1157675943285925</v>
+        <v>0.1172886289879097</v>
       </c>
       <c r="T55">
-        <v>1.28487576883232</v>
+        <v>1.312807850763457</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03654428148965523</v>
+        <v>0.0358675355361431</v>
       </c>
       <c r="W55">
-        <v>0.2271828584247393</v>
+        <v>0.2273424351205775</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1475033604451012</v>
+        <v>0.1447718167331549</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1767176842995503</v>
+        <v>0.1786176842995503</v>
       </c>
       <c r="C56">
-        <v>-129.6863941570394</v>
+        <v>-135.8973777862357</v>
       </c>
       <c r="D56">
-        <v>102.5150939086973</v>
+        <v>101.0485822807184</v>
       </c>
       <c r="E56">
-        <v>57.2542879440021</v>
+        <v>61.99875994521949</v>
       </c>
       <c r="F56">
-        <v>256.2014880657367</v>
+        <v>260.9459600669541</v>
       </c>
       <c r="G56">
         <v>24</v>
@@ -5861,37 +5861,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M56">
-        <v>60.41231088590071</v>
+        <v>61.53105738378777</v>
       </c>
       <c r="N56">
-        <v>-51.66631088590071</v>
+        <v>-52.78505738378777</v>
       </c>
       <c r="O56">
-        <v>-12.80044198890724</v>
+        <v>-13.07761389069294</v>
       </c>
       <c r="P56">
-        <v>-38.86586889699347</v>
+        <v>-39.70744349309483</v>
       </c>
       <c r="Q56">
-        <v>-33.83586889699347</v>
+        <v>-34.67744349309483</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1172886289879097</v>
+        <v>0.1188772651876411</v>
       </c>
       <c r="T56">
-        <v>1.312807850763457</v>
+        <v>1.341981358558201</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0358675355361431</v>
+        <v>0.03521539852639503</v>
       </c>
       <c r="W56">
-        <v>0.2273424351205775</v>
+        <v>0.2274962090274761</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1447718167331549</v>
+        <v>0.1421396018834611</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1786176842995503</v>
+        <v>0.1805176842995503</v>
       </c>
       <c r="C57">
-        <v>-135.8973777862357</v>
+        <v>-142.0669953229602</v>
       </c>
       <c r="D57">
-        <v>101.0485822807184</v>
+        <v>99.62343674521121</v>
       </c>
       <c r="E57">
-        <v>61.99875994521949</v>
+        <v>66.74323194643682</v>
       </c>
       <c r="F57">
-        <v>260.9459600669541</v>
+        <v>265.6904320681714</v>
       </c>
       <c r="G57">
         <v>24</v>
@@ -5943,37 +5943,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M57">
-        <v>61.53105738378777</v>
+        <v>62.64980388167481</v>
       </c>
       <c r="N57">
-        <v>-52.78505738378777</v>
+        <v>-53.90380388167482</v>
       </c>
       <c r="O57">
-        <v>-13.07761389069294</v>
+        <v>-13.35478579247864</v>
       </c>
       <c r="P57">
-        <v>-39.70744349309483</v>
+        <v>-40.54901808919617</v>
       </c>
       <c r="Q57">
-        <v>-34.67744349309483</v>
+        <v>-35.51901808919617</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1188772651876411</v>
+        <v>0.1205381121237238</v>
       </c>
       <c r="T57">
-        <v>1.341981358558201</v>
+        <v>1.372480934889069</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03521539852639503</v>
+        <v>0.03458655212413798</v>
       </c>
       <c r="W57">
-        <v>0.2274962090274761</v>
+        <v>0.2276444910091283</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1421396018834611</v>
+        <v>0.1396013947069707</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1805176842995503</v>
+        <v>0.1824176842995503</v>
       </c>
       <c r="C58">
-        <v>-142.0669953229602</v>
+        <v>-148.1969726545187</v>
       </c>
       <c r="D58">
-        <v>99.62343674521121</v>
+        <v>98.23793141487002</v>
       </c>
       <c r="E58">
-        <v>66.74323194643682</v>
+        <v>71.48770394765415</v>
       </c>
       <c r="F58">
-        <v>265.6904320681714</v>
+        <v>270.4349040693887</v>
       </c>
       <c r="G58">
         <v>24</v>
@@ -6025,37 +6025,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M58">
-        <v>62.64980388167481</v>
+        <v>63.76855037956187</v>
       </c>
       <c r="N58">
-        <v>-53.90380388167482</v>
+        <v>-55.02255037956186</v>
       </c>
       <c r="O58">
-        <v>-13.35478579247864</v>
+        <v>-13.63195769426434</v>
       </c>
       <c r="P58">
-        <v>-40.54901808919617</v>
+        <v>-41.39059268529752</v>
       </c>
       <c r="Q58">
-        <v>-35.51901808919617</v>
+        <v>-36.36059268529752</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1205381121237238</v>
+        <v>0.1222762077545081</v>
       </c>
       <c r="T58">
-        <v>1.372480934889069</v>
+        <v>1.404399096165559</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03458655212413798</v>
+        <v>0.03397977050792503</v>
       </c>
       <c r="W58">
-        <v>0.2276444910091283</v>
+        <v>0.2277875701142313</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1396013947069707</v>
+        <v>0.13715224743141</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1824176842995503</v>
+        <v>0.1843176842995503</v>
       </c>
       <c r="C59">
-        <v>-148.1969726545187</v>
+        <v>-154.2889409745788</v>
       </c>
       <c r="D59">
-        <v>98.23793141487002</v>
+        <v>96.89043509602735</v>
       </c>
       <c r="E59">
-        <v>71.48770394765415</v>
+        <v>76.23217594887154</v>
       </c>
       <c r="F59">
-        <v>270.4349040693887</v>
+        <v>275.1793760706061</v>
       </c>
       <c r="G59">
         <v>24</v>
@@ -6107,37 +6107,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M59">
-        <v>63.76855037956187</v>
+        <v>64.88729687744892</v>
       </c>
       <c r="N59">
-        <v>-55.02255037956186</v>
+        <v>-56.14129687744892</v>
       </c>
       <c r="O59">
-        <v>-13.63195769426434</v>
+        <v>-13.90912959605005</v>
       </c>
       <c r="P59">
-        <v>-41.39059268529752</v>
+        <v>-42.23216728139887</v>
       </c>
       <c r="Q59">
-        <v>-36.36059268529752</v>
+        <v>-37.20216728139887</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1222762077545081</v>
+        <v>0.1240970698439011</v>
       </c>
       <c r="T59">
-        <v>1.404399096165559</v>
+        <v>1.437837169883787</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03397977050792503</v>
+        <v>0.03339391239571943</v>
       </c>
       <c r="W59">
-        <v>0.2277875701142313</v>
+        <v>0.2279257154570894</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.13715224743141</v>
+        <v>0.1347875535101787</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1843176842995503</v>
+        <v>0.1862176842995503</v>
       </c>
       <c r="C60">
-        <v>-154.2889409745787</v>
+        <v>-160.3444431896951</v>
       </c>
       <c r="D60">
-        <v>96.89043509602735</v>
+        <v>95.57940488212832</v>
       </c>
       <c r="E60">
-        <v>76.23217594887149</v>
+        <v>80.97664795008882</v>
       </c>
       <c r="F60">
-        <v>275.1793760706061</v>
+        <v>279.9238480718234</v>
       </c>
       <c r="G60">
         <v>24</v>
@@ -6189,37 +6189,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M60">
-        <v>64.8872968774489</v>
+        <v>66.00604337533596</v>
       </c>
       <c r="N60">
-        <v>-56.14129687744891</v>
+        <v>-57.26004337533597</v>
       </c>
       <c r="O60">
-        <v>-13.90912959605004</v>
+        <v>-14.18630149783574</v>
       </c>
       <c r="P60">
-        <v>-42.23216728139887</v>
+        <v>-43.07374187750023</v>
       </c>
       <c r="Q60">
-        <v>-37.20216728139886</v>
+        <v>-38.04374187750022</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1240970698439011</v>
+        <v>0.1260067544742401</v>
       </c>
       <c r="T60">
-        <v>1.437837169883786</v>
+        <v>1.472906369149245</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.03339391239571943</v>
+        <v>0.03282791388053775</v>
       </c>
       <c r="W60">
-        <v>0.2279257154570894</v>
+        <v>0.2280591779069692</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1347875535101787</v>
+        <v>0.1325030187049214</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1862176842995503</v>
+        <v>0.1881176842995503</v>
       </c>
       <c r="C61">
-        <v>-160.3444431896951</v>
+        <v>-166.364939812658</v>
       </c>
       <c r="D61">
-        <v>95.57940488212832</v>
+        <v>94.30338026038271</v>
       </c>
       <c r="E61">
-        <v>80.97664795008882</v>
+        <v>85.72111995130615</v>
       </c>
       <c r="F61">
-        <v>279.9238480718234</v>
+        <v>284.6683200730407</v>
       </c>
       <c r="G61">
         <v>24</v>
@@ -6271,37 +6271,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M61">
-        <v>66.00604337533596</v>
+        <v>67.12478987322301</v>
       </c>
       <c r="N61">
-        <v>-57.26004337533597</v>
+        <v>-58.37878987322301</v>
       </c>
       <c r="O61">
-        <v>-14.18630149783574</v>
+        <v>-14.46347339962144</v>
       </c>
       <c r="P61">
-        <v>-43.07374187750023</v>
+        <v>-43.91531647360157</v>
       </c>
       <c r="Q61">
-        <v>-38.04374187750022</v>
+        <v>-38.88531647360157</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1260067544742401</v>
+        <v>0.1280119233360962</v>
       </c>
       <c r="T61">
-        <v>1.472906369149245</v>
+        <v>1.509729028377976</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03282791388053775</v>
+        <v>0.03228078198252879</v>
       </c>
       <c r="W61">
-        <v>0.2280591779069692</v>
+        <v>0.2281881916085197</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1325030187049214</v>
+        <v>0.1302946350598394</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1881176842995503</v>
+        <v>0.1900176842995503</v>
       </c>
       <c r="C62">
-        <v>-166.364939812658</v>
+        <v>-172.3518143899879</v>
       </c>
       <c r="D62">
-        <v>94.30338026038271</v>
+        <v>93.06097768427026</v>
       </c>
       <c r="E62">
-        <v>85.72111995130615</v>
+        <v>90.46559195252354</v>
       </c>
       <c r="F62">
-        <v>284.6683200730407</v>
+        <v>289.4127920742581</v>
       </c>
       <c r="G62">
         <v>24</v>
@@ -6353,37 +6353,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M62">
-        <v>67.12478987322301</v>
+        <v>68.24353637111007</v>
       </c>
       <c r="N62">
-        <v>-58.37878987322301</v>
+        <v>-59.49753637111007</v>
       </c>
       <c r="O62">
-        <v>-14.46347339962144</v>
+        <v>-14.74064530140715</v>
       </c>
       <c r="P62">
-        <v>-43.91531647360157</v>
+        <v>-44.75689106970292</v>
       </c>
       <c r="Q62">
-        <v>-38.88531647360157</v>
+        <v>-39.72689106970292</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1280119233360962</v>
+        <v>0.130119921370355</v>
       </c>
       <c r="T62">
-        <v>1.509729028377976</v>
+        <v>1.548440029105616</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03228078198252879</v>
+        <v>0.03175158883527421</v>
       </c>
       <c r="W62">
-        <v>0.2281881916085197</v>
+        <v>0.2283129753526424</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1302946350598394</v>
+        <v>0.1281586574359076</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1900176842995503</v>
+        <v>0.1919176842995503</v>
       </c>
       <c r="C63">
-        <v>-172.3518143899879</v>
+        <v>-178.3063785059805</v>
       </c>
       <c r="D63">
-        <v>93.06097768427026</v>
+        <v>91.85088556949496</v>
       </c>
       <c r="E63">
-        <v>90.46559195252354</v>
+        <v>95.21006395374087</v>
       </c>
       <c r="F63">
-        <v>289.4127920742581</v>
+        <v>294.1572640754754</v>
       </c>
       <c r="G63">
         <v>24</v>
@@ -6435,37 +6435,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M63">
-        <v>68.24353637111007</v>
+        <v>69.36228286899711</v>
       </c>
       <c r="N63">
-        <v>-59.49753637111007</v>
+        <v>-60.61628286899712</v>
       </c>
       <c r="O63">
-        <v>-14.74064530140715</v>
+        <v>-15.01781720319284</v>
       </c>
       <c r="P63">
-        <v>-44.75689106970292</v>
+        <v>-45.59846566580427</v>
       </c>
       <c r="Q63">
-        <v>-39.72689106970292</v>
+        <v>-40.56846566580427</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.130119921370355</v>
+        <v>0.1323388666695749</v>
       </c>
       <c r="T63">
-        <v>1.548440029105616</v>
+        <v>1.589188450924185</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03175158883527421</v>
+        <v>0.03123946643470527</v>
       </c>
       <c r="W63">
-        <v>0.2283129753526424</v>
+        <v>0.2284337338146965</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1281586574359076</v>
+        <v>0.1260915823159736</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1919176842995503</v>
+        <v>0.1938176842995503</v>
       </c>
       <c r="C64">
-        <v>-178.3063785059805</v>
+        <v>-184.2298764013529</v>
       </c>
       <c r="D64">
-        <v>91.85088556949496</v>
+        <v>90.6718596753399</v>
       </c>
       <c r="E64">
-        <v>95.21006395374087</v>
+        <v>99.9545359549582</v>
       </c>
       <c r="F64">
-        <v>294.1572640754754</v>
+        <v>298.9017360766928</v>
       </c>
       <c r="G64">
         <v>24</v>
@@ -6517,37 +6517,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M64">
-        <v>69.36228286899711</v>
+        <v>70.48102936688416</v>
       </c>
       <c r="N64">
-        <v>-60.61628286899712</v>
+        <v>-61.73502936688416</v>
       </c>
       <c r="O64">
-        <v>-15.01781720319284</v>
+        <v>-15.29498910497854</v>
       </c>
       <c r="P64">
-        <v>-45.59846566580427</v>
+        <v>-46.44004026190562</v>
       </c>
       <c r="Q64">
-        <v>-40.56846566580427</v>
+        <v>-41.41004026190562</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1323388666695749</v>
+        <v>0.1346777549579418</v>
       </c>
       <c r="T64">
-        <v>1.589188450924185</v>
+        <v>1.632139490138352</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03123946643470527</v>
+        <v>0.03074360188812265</v>
       </c>
       <c r="W64">
-        <v>0.2284337338146965</v>
+        <v>0.2285506586747807</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1260915823159736</v>
+        <v>0.1240901286284185</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1938176842995503</v>
+        <v>0.1957176842995503</v>
       </c>
       <c r="C65">
-        <v>-184.2298764013529</v>
+        <v>-190.1234892406779</v>
       </c>
       <c r="D65">
-        <v>90.6718596753399</v>
+        <v>89.52271883723223</v>
       </c>
       <c r="E65">
-        <v>99.9545359549582</v>
+        <v>104.6990079561755</v>
       </c>
       <c r="F65">
-        <v>298.9017360766928</v>
+        <v>303.6462080779101</v>
       </c>
       <c r="G65">
         <v>24</v>
@@ -6599,37 +6599,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M65">
-        <v>70.48102936688416</v>
+        <v>71.5997758647712</v>
       </c>
       <c r="N65">
-        <v>-61.73502936688416</v>
+        <v>-62.85377586477121</v>
       </c>
       <c r="O65">
-        <v>-15.29498910497854</v>
+        <v>-15.57216100676424</v>
       </c>
       <c r="P65">
-        <v>-46.44004026190562</v>
+        <v>-47.28161485800696</v>
       </c>
       <c r="Q65">
-        <v>-41.41004026190562</v>
+        <v>-42.25161485800696</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1346777549579418</v>
+        <v>0.1371465814845513</v>
       </c>
       <c r="T65">
-        <v>1.632139490138352</v>
+        <v>1.677476698197751</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03074360188812265</v>
+        <v>0.03026323310862074</v>
       </c>
       <c r="W65">
-        <v>0.2285506586747807</v>
+        <v>0.2286639296329872</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1240901286284185</v>
+        <v>0.1221512203685995</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1957176842995503</v>
+        <v>0.1976176842995503</v>
       </c>
       <c r="C66">
-        <v>-190.1234892406779</v>
+        <v>-195.9883390593775</v>
       </c>
       <c r="D66">
-        <v>89.52271883723223</v>
+        <v>88.40234101975</v>
       </c>
       <c r="E66">
-        <v>104.6990079561755</v>
+        <v>109.4434799573929</v>
       </c>
       <c r="F66">
-        <v>303.6462080779101</v>
+        <v>308.3906800791275</v>
       </c>
       <c r="G66">
         <v>24</v>
@@ -6681,37 +6681,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M66">
-        <v>71.5997758647712</v>
+        <v>72.71852236265826</v>
       </c>
       <c r="N66">
-        <v>-62.85377586477121</v>
+        <v>-63.97252236265827</v>
       </c>
       <c r="O66">
-        <v>-15.57216100676424</v>
+        <v>-15.84933290854995</v>
       </c>
       <c r="P66">
-        <v>-47.28161485800696</v>
+        <v>-48.12318945410832</v>
       </c>
       <c r="Q66">
-        <v>-42.25161485800696</v>
+        <v>-43.09318945410832</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1371465814845513</v>
+        <v>0.1397564838126813</v>
       </c>
       <c r="T66">
-        <v>1.677476698197751</v>
+        <v>1.725404603860544</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03026323310862074</v>
+        <v>0.02979764490694965</v>
       </c>
       <c r="W66">
-        <v>0.2286639296329872</v>
+        <v>0.2287737153309413</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1221512203685995</v>
+        <v>0.1202719708244672</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1976176842995503</v>
+        <v>0.1995176842995503</v>
       </c>
       <c r="C67">
-        <v>-195.9883390593775</v>
+        <v>-201.8254924179994</v>
       </c>
       <c r="D67">
-        <v>88.40234101975</v>
+        <v>87.30965966234537</v>
       </c>
       <c r="E67">
-        <v>109.4434799573929</v>
+        <v>114.1879519586103</v>
       </c>
       <c r="F67">
-        <v>308.3906800791275</v>
+        <v>313.1351520803448</v>
       </c>
       <c r="G67">
         <v>24</v>
@@ -6763,37 +6763,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M67">
-        <v>72.71852236265826</v>
+        <v>73.83726886054531</v>
       </c>
       <c r="N67">
-        <v>-63.97252236265827</v>
+        <v>-65.09126886054531</v>
       </c>
       <c r="O67">
-        <v>-15.84933290854995</v>
+        <v>-16.12650481033564</v>
       </c>
       <c r="P67">
-        <v>-48.12318945410832</v>
+        <v>-48.96476405020967</v>
       </c>
       <c r="Q67">
-        <v>-43.09318945410832</v>
+        <v>-43.93476405020967</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1397564838126813</v>
+        <v>0.1425199098071719</v>
       </c>
       <c r="T67">
-        <v>1.725404603860544</v>
+        <v>1.776151798091737</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02979764490694965</v>
+        <v>0.02934616543866253</v>
       </c>
       <c r="W67">
-        <v>0.2287737153309413</v>
+        <v>0.2288801741895634</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1202719708244672</v>
+        <v>0.1184496682362176</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1995176842995503</v>
+        <v>0.2014176842995503</v>
       </c>
       <c r="C68">
-        <v>-201.8254924179994</v>
+        <v>-207.6359637887945</v>
       </c>
       <c r="D68">
-        <v>87.30965966234537</v>
+        <v>86.24366029276767</v>
       </c>
       <c r="E68">
-        <v>114.1879519586103</v>
+        <v>118.9324239598276</v>
       </c>
       <c r="F68">
-        <v>313.1351520803448</v>
+        <v>317.8796240815622</v>
       </c>
       <c r="G68">
         <v>24</v>
@@ -6845,37 +6845,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M68">
-        <v>73.83726886054531</v>
+        <v>74.95601535843235</v>
       </c>
       <c r="N68">
-        <v>-65.09126886054531</v>
+        <v>-66.21001535843236</v>
       </c>
       <c r="O68">
-        <v>-16.12650481033564</v>
+        <v>-16.40367671212134</v>
       </c>
       <c r="P68">
-        <v>-48.96476405020967</v>
+        <v>-49.80633864631102</v>
       </c>
       <c r="Q68">
-        <v>-43.93476405020967</v>
+        <v>-44.77633864631102</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1425199098071719</v>
+        <v>0.1454508161649651</v>
       </c>
       <c r="T68">
-        <v>1.776151798091737</v>
+        <v>1.829974579852092</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.02934616543866253</v>
+        <v>0.02890816296942877</v>
       </c>
       <c r="W68">
-        <v>0.2288801741895634</v>
+        <v>0.2289834551718087</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1184496682362176</v>
+        <v>0.1166817627401547</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2014176842995503</v>
+        <v>0.2033176842995503</v>
       </c>
       <c r="C69">
-        <v>-207.6359637887945</v>
+        <v>-213.4207186971973</v>
       </c>
       <c r="D69">
-        <v>86.24366029276767</v>
+        <v>85.20337738558223</v>
       </c>
       <c r="E69">
-        <v>118.9324239598276</v>
+        <v>123.676895961045</v>
       </c>
       <c r="F69">
-        <v>317.8796240815622</v>
+        <v>322.6240960827795</v>
       </c>
       <c r="G69">
         <v>24</v>
@@ -6927,37 +6927,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M69">
-        <v>74.95601535843235</v>
+        <v>76.07476185631943</v>
       </c>
       <c r="N69">
-        <v>-66.21001535843236</v>
+        <v>-67.32876185631943</v>
       </c>
       <c r="O69">
-        <v>-16.40367671212134</v>
+        <v>-16.68084861390705</v>
       </c>
       <c r="P69">
-        <v>-49.80633864631102</v>
+        <v>-50.64791324241239</v>
       </c>
       <c r="Q69">
-        <v>-44.77633864631102</v>
+        <v>-45.61791324241238</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1454508161649651</v>
+        <v>0.1485649041701202</v>
       </c>
       <c r="T69">
-        <v>1.829974579852092</v>
+        <v>1.88716128547247</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02890816296942877</v>
+        <v>0.02848304292576069</v>
       </c>
       <c r="W69">
-        <v>0.2289834551718087</v>
+        <v>0.2290836984781056</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1166817627401547</v>
+        <v>0.1149658544645642</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2033176842995503</v>
+        <v>0.2052176842995503</v>
       </c>
       <c r="C70">
-        <v>-213.4207186971973</v>
+        <v>-219.1806766386596</v>
       </c>
       <c r="D70">
-        <v>85.20337738558223</v>
+        <v>84.18789144533723</v>
       </c>
       <c r="E70">
-        <v>123.676895961045</v>
+        <v>128.4213679622623</v>
       </c>
       <c r="F70">
-        <v>322.6240960827795</v>
+        <v>327.3685680839969</v>
       </c>
       <c r="G70">
         <v>24</v>
@@ -7009,37 +7009,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M70">
-        <v>76.07476185631943</v>
+        <v>77.19350835420647</v>
       </c>
       <c r="N70">
-        <v>-67.32876185631943</v>
+        <v>-68.44750835420648</v>
       </c>
       <c r="O70">
-        <v>-16.68084861390705</v>
+        <v>-16.95802051569275</v>
       </c>
       <c r="P70">
-        <v>-50.64791324241239</v>
+        <v>-51.48948783851372</v>
       </c>
       <c r="Q70">
-        <v>-45.61791324241238</v>
+        <v>-46.45948783851372</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1485649041701202</v>
+        <v>0.1518799010788338</v>
       </c>
       <c r="T70">
-        <v>1.88716128547247</v>
+        <v>1.948037455971582</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02848304292576069</v>
+        <v>0.02807024520219894</v>
       </c>
       <c r="W70">
-        <v>0.2290836984781056</v>
+        <v>0.2291810361813215</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1149658544645642</v>
+        <v>0.1132996826607299</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2052176842995503</v>
+        <v>0.2071176842995503</v>
       </c>
       <c r="C71">
-        <v>-219.1806766386596</v>
+        <v>-224.9167137893563</v>
       </c>
       <c r="D71">
-        <v>84.18789144533723</v>
+        <v>83.19632629585794</v>
       </c>
       <c r="E71">
-        <v>128.4213679622623</v>
+        <v>133.1658399634796</v>
       </c>
       <c r="F71">
-        <v>327.3685680839969</v>
+        <v>332.1130400852142</v>
       </c>
       <c r="G71">
         <v>24</v>
@@ -7091,37 +7091,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M71">
-        <v>77.19350835420647</v>
+        <v>78.31225485209352</v>
       </c>
       <c r="N71">
-        <v>-68.44750835420648</v>
+        <v>-69.56625485209352</v>
       </c>
       <c r="O71">
-        <v>-16.95802051569275</v>
+        <v>-17.23519241747845</v>
       </c>
       <c r="P71">
-        <v>-51.48948783851372</v>
+        <v>-52.33106243461508</v>
       </c>
       <c r="Q71">
-        <v>-46.45948783851372</v>
+        <v>-47.30106243461508</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1518799010788338</v>
+        <v>0.1554158977814616</v>
       </c>
       <c r="T71">
-        <v>1.948037455971582</v>
+        <v>2.012972037837302</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02807024520219894</v>
+        <v>0.02766924169931038</v>
       </c>
       <c r="W71">
-        <v>0.2291810361813215</v>
+        <v>0.2292755928073026</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1132996826607299</v>
+        <v>0.1116811157655766</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2071176842995503</v>
+        <v>0.2090176842995503</v>
       </c>
       <c r="C72">
-        <v>-224.9167137893563</v>
+        <v>-230.6296655275611</v>
       </c>
       <c r="D72">
-        <v>83.19632629585794</v>
+        <v>82.22784655887048</v>
       </c>
       <c r="E72">
-        <v>133.1658399634796</v>
+        <v>137.910311964697</v>
       </c>
       <c r="F72">
-        <v>332.1130400852142</v>
+        <v>336.8575120864316</v>
       </c>
       <c r="G72">
         <v>24</v>
@@ -7173,37 +7173,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M72">
-        <v>78.31225485209352</v>
+        <v>79.43100134998058</v>
       </c>
       <c r="N72">
-        <v>-69.56625485209352</v>
+        <v>-70.68500134998058</v>
       </c>
       <c r="O72">
-        <v>-17.23519241747845</v>
+        <v>-17.51236431926415</v>
       </c>
       <c r="P72">
-        <v>-52.33106243461508</v>
+        <v>-53.17263703071643</v>
       </c>
       <c r="Q72">
-        <v>-47.30106243461508</v>
+        <v>-48.14263703071643</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1554158977814616</v>
+        <v>0.1591957563256499</v>
       </c>
       <c r="T72">
-        <v>2.012972037837302</v>
+        <v>2.082384866728243</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02766924169931038</v>
+        <v>0.02727953406974263</v>
       </c>
       <c r="W72">
-        <v>0.2292755928073026</v>
+        <v>0.2293674858663547</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1116811157655766</v>
+        <v>0.1101081423040896</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2090176842995503</v>
+        <v>0.2109176842995503</v>
       </c>
       <c r="C73">
-        <v>-230.6296655275611</v>
+        <v>-236.3203287809426</v>
       </c>
       <c r="D73">
-        <v>82.22784655887048</v>
+        <v>81.28165530670621</v>
       </c>
       <c r="E73">
-        <v>137.910311964697</v>
+        <v>142.6547839659143</v>
       </c>
       <c r="F73">
-        <v>336.8575120864315</v>
+        <v>341.6019840876489</v>
       </c>
       <c r="G73">
         <v>24</v>
@@ -7255,37 +7255,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M73">
-        <v>79.43100134998056</v>
+        <v>80.54974784786761</v>
       </c>
       <c r="N73">
-        <v>-70.68500134998057</v>
+        <v>-71.80374784786761</v>
       </c>
       <c r="O73">
-        <v>-17.51236431926415</v>
+        <v>-17.78953622104985</v>
       </c>
       <c r="P73">
-        <v>-53.17263703071642</v>
+        <v>-54.01421162681777</v>
       </c>
       <c r="Q73">
-        <v>-48.14263703071641</v>
+        <v>-48.98421162681777</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1591957563256499</v>
+        <v>0.1632456047658516</v>
       </c>
       <c r="T73">
-        <v>2.082384866728243</v>
+        <v>2.15675575482568</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02727953406974264</v>
+        <v>0.02690065165210732</v>
       </c>
       <c r="W73">
-        <v>0.2293674858663547</v>
+        <v>0.2294568263404331</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1101081423040896</v>
+        <v>0.1085788625498662</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2109176842995503</v>
+        <v>0.2128176842995503</v>
       </c>
       <c r="C74">
-        <v>-236.3203287809426</v>
+        <v>-241.9894642136428</v>
       </c>
       <c r="D74">
-        <v>81.28165530670621</v>
+        <v>80.35699187522339</v>
       </c>
       <c r="E74">
-        <v>142.6547839659143</v>
+        <v>147.3992559671316</v>
       </c>
       <c r="F74">
-        <v>341.6019840876489</v>
+        <v>346.3464560888662</v>
       </c>
       <c r="G74">
         <v>24</v>
@@ -7337,37 +7337,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M74">
-        <v>80.54974784786761</v>
+        <v>81.66849434575465</v>
       </c>
       <c r="N74">
-        <v>-71.80374784786761</v>
+        <v>-72.92249434575466</v>
       </c>
       <c r="O74">
-        <v>-17.78953622104985</v>
+        <v>-18.06670812283554</v>
       </c>
       <c r="P74">
-        <v>-54.01421162681777</v>
+        <v>-54.85578622291911</v>
       </c>
       <c r="Q74">
-        <v>-48.98421162681777</v>
+        <v>-49.82578622291911</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1632456047658516</v>
+        <v>0.1675954419794017</v>
       </c>
       <c r="T74">
-        <v>2.15675575482568</v>
+        <v>2.236635597597001</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02690065165210732</v>
+        <v>0.0265321495746812</v>
       </c>
       <c r="W74">
-        <v>0.2294568263404331</v>
+        <v>0.2295437191302902</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1085788625498662</v>
+        <v>0.1070914808711009</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2128176842995503</v>
+        <v>0.2147176842995503</v>
       </c>
       <c r="C75">
-        <v>-241.9894642136428</v>
+        <v>-247.6377982657523</v>
       </c>
       <c r="D75">
-        <v>80.35699187522339</v>
+        <v>79.45312982433134</v>
       </c>
       <c r="E75">
-        <v>147.3992559671316</v>
+        <v>152.143727968349</v>
       </c>
       <c r="F75">
-        <v>346.3464560888662</v>
+        <v>351.0909280900836</v>
       </c>
       <c r="G75">
         <v>24</v>
@@ -7419,37 +7419,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M75">
-        <v>81.66849434575465</v>
+        <v>82.78724084364171</v>
       </c>
       <c r="N75">
-        <v>-72.92249434575466</v>
+        <v>-74.04124084364172</v>
       </c>
       <c r="O75">
-        <v>-18.06670812283554</v>
+        <v>-18.34388002462125</v>
       </c>
       <c r="P75">
-        <v>-54.85578622291911</v>
+        <v>-55.69736081902047</v>
       </c>
       <c r="Q75">
-        <v>-49.82578622291911</v>
+        <v>-50.66736081902047</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1675954419794017</v>
+        <v>0.1722798820555325</v>
       </c>
       <c r="T75">
-        <v>2.236635597597001</v>
+        <v>2.322660043658424</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0265321495746812</v>
+        <v>0.02617360701286118</v>
       </c>
       <c r="W75">
-        <v>0.2295437191302902</v>
+        <v>0.2296282634663673</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1070914808711009</v>
+        <v>0.1056442986971671</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2147176842995503</v>
+        <v>0.2166176842995503</v>
       </c>
       <c r="C76">
-        <v>-247.6377982657523</v>
+        <v>-253.2660250566757</v>
       </c>
       <c r="D76">
-        <v>79.45312982433134</v>
+        <v>78.56937503462522</v>
       </c>
       <c r="E76">
-        <v>152.143727968349</v>
+        <v>156.8881999695664</v>
       </c>
       <c r="F76">
-        <v>351.0909280900836</v>
+        <v>355.8354000913009</v>
       </c>
       <c r="G76">
         <v>24</v>
@@ -7501,37 +7501,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M76">
-        <v>82.78724084364171</v>
+        <v>83.90598734152876</v>
       </c>
       <c r="N76">
-        <v>-74.04124084364172</v>
+        <v>-75.15998734152876</v>
       </c>
       <c r="O76">
-        <v>-18.34388002462125</v>
+        <v>-18.62105192640695</v>
       </c>
       <c r="P76">
-        <v>-55.69736081902047</v>
+        <v>-56.53893541512181</v>
       </c>
       <c r="Q76">
-        <v>-50.66736081902047</v>
+        <v>-51.50893541512181</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1722798820555325</v>
+        <v>0.1773390773377539</v>
       </c>
       <c r="T76">
-        <v>2.322660043658424</v>
+        <v>2.415566445404762</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02617360701286118</v>
+        <v>0.02582462558602303</v>
       </c>
       <c r="W76">
-        <v>0.2296282634663673</v>
+        <v>0.2297105532868158</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1056442986971671</v>
+        <v>0.1042357080478715</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2166176842995503</v>
+        <v>0.2185176842995503</v>
       </c>
       <c r="C77">
-        <v>-253.2660250566757</v>
+        <v>-258.8748081628687</v>
       </c>
       <c r="D77">
-        <v>78.56937503462522</v>
+        <v>77.70506392964955</v>
       </c>
       <c r="E77">
-        <v>156.8881999695664</v>
+        <v>161.6326719707837</v>
       </c>
       <c r="F77">
-        <v>355.8354000913009</v>
+        <v>360.5798720925183</v>
       </c>
       <c r="G77">
         <v>24</v>
@@ -7583,37 +7583,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M77">
-        <v>83.90598734152876</v>
+        <v>85.0247338394158</v>
       </c>
       <c r="N77">
-        <v>-75.15998734152876</v>
+        <v>-76.27873383941581</v>
       </c>
       <c r="O77">
-        <v>-18.62105192640695</v>
+        <v>-18.89822382819264</v>
       </c>
       <c r="P77">
-        <v>-56.53893541512181</v>
+        <v>-57.38051001122317</v>
       </c>
       <c r="Q77">
-        <v>-51.50893541512181</v>
+        <v>-52.35051001122316</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1773390773377539</v>
+        <v>0.1828198722268269</v>
       </c>
       <c r="T77">
-        <v>2.415566445404762</v>
+        <v>2.516215047296626</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02582462558602303</v>
+        <v>0.02548482788094378</v>
       </c>
       <c r="W77">
-        <v>0.2297105532868158</v>
+        <v>0.2297906775856735</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1042357080478715</v>
+        <v>0.1028641855735575</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2185176842995503</v>
+        <v>0.2204176842995503</v>
       </c>
       <c r="C78">
-        <v>-258.8748081628687</v>
+        <v>-264.4647822795137</v>
       </c>
       <c r="D78">
-        <v>77.70506392964955</v>
+        <v>76.85956181422199</v>
       </c>
       <c r="E78">
-        <v>161.6326719707837</v>
+        <v>166.3771439720011</v>
       </c>
       <c r="F78">
-        <v>360.5798720925183</v>
+        <v>365.3243440937356</v>
       </c>
       <c r="G78">
         <v>24</v>
@@ -7665,37 +7665,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M78">
-        <v>85.0247338394158</v>
+        <v>86.14348033730288</v>
       </c>
       <c r="N78">
-        <v>-76.27873383941581</v>
+        <v>-77.39748033730288</v>
       </c>
       <c r="O78">
-        <v>-18.89822382819264</v>
+        <v>-19.17539572997835</v>
       </c>
       <c r="P78">
-        <v>-57.38051001122317</v>
+        <v>-58.22208460732453</v>
       </c>
       <c r="Q78">
-        <v>-52.35051001122316</v>
+        <v>-53.19208460732453</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1828198722268269</v>
+        <v>0.1887772579758194</v>
       </c>
       <c r="T78">
-        <v>2.516215047296626</v>
+        <v>2.625615701526915</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02548482788094378</v>
+        <v>0.02515385609028217</v>
       </c>
       <c r="W78">
-        <v>0.2297906775856735</v>
+        <v>0.2298687207339115</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1028641855735575</v>
+        <v>0.1015282870596151</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2204176842995503</v>
+        <v>0.2223176842995503</v>
       </c>
       <c r="C79">
-        <v>-264.4647822795137</v>
+        <v>-270.0365547748798</v>
       </c>
       <c r="D79">
-        <v>76.85956181422199</v>
+        <v>76.03226132007318</v>
       </c>
       <c r="E79">
-        <v>166.3771439720011</v>
+        <v>171.1216159732184</v>
       </c>
       <c r="F79">
-        <v>365.3243440937356</v>
+        <v>370.068816094953</v>
       </c>
       <c r="G79">
         <v>24</v>
@@ -7747,37 +7747,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M79">
-        <v>86.14348033730288</v>
+        <v>87.26222683518992</v>
       </c>
       <c r="N79">
-        <v>-77.39748033730288</v>
+        <v>-78.51622683518993</v>
       </c>
       <c r="O79">
-        <v>-19.17539572997835</v>
+        <v>-19.45256763176405</v>
       </c>
       <c r="P79">
-        <v>-58.22208460732453</v>
+        <v>-59.06365920342587</v>
       </c>
       <c r="Q79">
-        <v>-53.19208460732453</v>
+        <v>-54.03365920342587</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1887772579758194</v>
+        <v>0.1952762242474476</v>
       </c>
       <c r="T79">
-        <v>2.625615701526915</v>
+        <v>2.744961869778138</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02515385609028217</v>
+        <v>0.02483137075579137</v>
       </c>
       <c r="W79">
-        <v>0.2298687207339115</v>
+        <v>0.2299447627757844</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1015282870596151</v>
+        <v>0.1002266423537226</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2223176842995503</v>
+        <v>0.2242176842995503</v>
       </c>
       <c r="C80">
-        <v>-270.0365547748798</v>
+        <v>-275.5907071453681</v>
       </c>
       <c r="D80">
-        <v>76.03226132007318</v>
+        <v>75.22258095080217</v>
       </c>
       <c r="E80">
-        <v>171.1216159732184</v>
+        <v>175.8660879744357</v>
       </c>
       <c r="F80">
-        <v>370.068816094953</v>
+        <v>374.8132880961703</v>
       </c>
       <c r="G80">
         <v>24</v>
@@ -7829,37 +7829,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M80">
-        <v>87.26222683518992</v>
+        <v>88.38097333307697</v>
       </c>
       <c r="N80">
-        <v>-78.51622683518993</v>
+        <v>-79.63497333307697</v>
       </c>
       <c r="O80">
-        <v>-19.45256763176405</v>
+        <v>-19.72973953354975</v>
       </c>
       <c r="P80">
-        <v>-59.06365920342587</v>
+        <v>-59.90523379952722</v>
       </c>
       <c r="Q80">
-        <v>-54.03365920342587</v>
+        <v>-54.87523379952722</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1952762242474476</v>
+        <v>0.2023941396878022</v>
       </c>
       <c r="T80">
-        <v>2.744961869778138</v>
+        <v>2.875674339767574</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02483137075579137</v>
+        <v>0.02451704960698389</v>
       </c>
       <c r="W80">
-        <v>0.2299447627757844</v>
+        <v>0.2300188797026732</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1002266423537226</v>
+        <v>0.098957950678359</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2242176842995503</v>
+        <v>0.2261176842995503</v>
       </c>
       <c r="C81">
-        <v>-275.5907071453681</v>
+        <v>-281.1277963785654</v>
       </c>
       <c r="D81">
-        <v>75.22258095080217</v>
+        <v>74.42996371882231</v>
       </c>
       <c r="E81">
-        <v>175.8660879744357</v>
+        <v>180.6105599756531</v>
       </c>
       <c r="F81">
-        <v>374.8132880961703</v>
+        <v>379.5577600973877</v>
       </c>
       <c r="G81">
         <v>24</v>
@@ -7911,37 +7911,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M81">
-        <v>88.38097333307697</v>
+        <v>89.49971983096403</v>
       </c>
       <c r="N81">
-        <v>-79.63497333307697</v>
+        <v>-80.75371983096403</v>
       </c>
       <c r="O81">
-        <v>-19.72973953354975</v>
+        <v>-20.00691143533545</v>
       </c>
       <c r="P81">
-        <v>-59.90523379952722</v>
+        <v>-60.74680839562858</v>
       </c>
       <c r="Q81">
-        <v>-54.87523379952722</v>
+        <v>-55.71680839562858</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2023941396878022</v>
+        <v>0.2102238466721923</v>
       </c>
       <c r="T81">
-        <v>2.875674339767574</v>
+        <v>3.019458056755952</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02451704960698389</v>
+        <v>0.02421058648689658</v>
       </c>
       <c r="W81">
-        <v>0.2300188797026732</v>
+        <v>0.2300911437063898</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.098957950678359</v>
+        <v>0.09772097629487952</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2261176842995503</v>
+        <v>0.2280176842995503</v>
       </c>
       <c r="C82">
-        <v>-281.1277963785654</v>
+        <v>-286.6483562310216</v>
       </c>
       <c r="D82">
-        <v>74.42996371882231</v>
+        <v>73.65387586758342</v>
       </c>
       <c r="E82">
-        <v>180.6105599756531</v>
+        <v>185.3550319768705</v>
       </c>
       <c r="F82">
-        <v>379.5577600973877</v>
+        <v>384.302232098605</v>
       </c>
       <c r="G82">
         <v>24</v>
@@ -7993,37 +7993,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M82">
-        <v>89.49971983096403</v>
+        <v>90.61846632885107</v>
       </c>
       <c r="N82">
-        <v>-80.75371983096403</v>
+        <v>-81.87246632885108</v>
       </c>
       <c r="O82">
-        <v>-20.00691143533545</v>
+        <v>-20.28408333712115</v>
       </c>
       <c r="P82">
-        <v>-60.74680839562858</v>
+        <v>-61.58838299172993</v>
       </c>
       <c r="Q82">
-        <v>-55.71680839562858</v>
+        <v>-56.55838299172993</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2102238466721923</v>
+        <v>0.2188777333391499</v>
       </c>
       <c r="T82">
-        <v>3.019458056755952</v>
+        <v>3.178376901848372</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02421058648689658</v>
+        <v>0.02391169035742873</v>
       </c>
       <c r="W82">
-        <v>0.2300911437063898</v>
+        <v>0.2301616234137183</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.09772097629487952</v>
+        <v>0.09651454448876995</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2280176842995503</v>
+        <v>0.2299176842995503</v>
       </c>
       <c r="C83">
-        <v>-286.6483562310216</v>
+        <v>-292.1528984269125</v>
       </c>
       <c r="D83">
-        <v>73.65387586758342</v>
+        <v>72.89380567290982</v>
       </c>
       <c r="E83">
-        <v>185.3550319768705</v>
+        <v>190.0995039780878</v>
       </c>
       <c r="F83">
-        <v>384.302232098605</v>
+        <v>389.0467040998224</v>
       </c>
       <c r="G83">
         <v>24</v>
@@ -8075,37 +8075,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M83">
-        <v>90.61846632885107</v>
+        <v>91.73721282673812</v>
       </c>
       <c r="N83">
-        <v>-81.87246632885108</v>
+        <v>-82.99121282673812</v>
       </c>
       <c r="O83">
-        <v>-20.28408333712115</v>
+        <v>-20.56125523890685</v>
       </c>
       <c r="P83">
-        <v>-61.58838299172993</v>
+        <v>-62.42995758783127</v>
       </c>
       <c r="Q83">
-        <v>-56.55838299172993</v>
+        <v>-57.39995758783127</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2188777333391499</v>
+        <v>0.2284931629691026</v>
       </c>
       <c r="T83">
-        <v>3.178376901848372</v>
+        <v>3.354953396395503</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02391169035742873</v>
+        <v>0.02362008437746008</v>
       </c>
       <c r="W83">
-        <v>0.2301616234137183</v>
+        <v>0.2302303841037949</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.09651454448876995</v>
+        <v>0.09533753784866295</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2299176842995503</v>
+        <v>0.2318176842995503</v>
       </c>
       <c r="C84">
-        <v>-292.1528984269125</v>
+        <v>-297.6419137832418</v>
       </c>
       <c r="D84">
-        <v>72.89380567290982</v>
+        <v>72.14926231779798</v>
       </c>
       <c r="E84">
-        <v>190.0995039780878</v>
+        <v>194.8439759793052</v>
       </c>
       <c r="F84">
-        <v>389.0467040998224</v>
+        <v>393.7911761010398</v>
       </c>
       <c r="G84">
         <v>24</v>
@@ -8157,37 +8157,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M84">
-        <v>91.73721282673812</v>
+        <v>92.85595932462518</v>
       </c>
       <c r="N84">
-        <v>-82.99121282673812</v>
+        <v>-84.10995932462518</v>
       </c>
       <c r="O84">
-        <v>-20.56125523890685</v>
+        <v>-20.83842714069255</v>
       </c>
       <c r="P84">
-        <v>-62.42995758783127</v>
+        <v>-63.27153218393263</v>
       </c>
       <c r="Q84">
-        <v>-57.39995758783127</v>
+        <v>-58.24153218393263</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2284931629691026</v>
+        <v>0.239239819614344</v>
       </c>
       <c r="T84">
-        <v>3.354953396395503</v>
+        <v>3.552303596183474</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02362008437746008</v>
+        <v>0.02333550504761117</v>
       </c>
       <c r="W84">
-        <v>0.2302303841037949</v>
+        <v>0.2302974879097733</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.09533753784866295</v>
+        <v>0.09418889281434173</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2318176842995503</v>
+        <v>0.2337176842995503</v>
       </c>
       <c r="C85">
-        <v>-297.6419137832418</v>
+        <v>-303.115873266783</v>
       </c>
       <c r="D85">
-        <v>72.14926231779798</v>
+        <v>71.41977483547407</v>
       </c>
       <c r="E85">
-        <v>194.8439759793052</v>
+        <v>199.5884479805225</v>
       </c>
       <c r="F85">
-        <v>393.7911761010398</v>
+        <v>398.5356481022571</v>
       </c>
       <c r="G85">
         <v>24</v>
@@ -8239,37 +8239,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M85">
-        <v>92.85595932462518</v>
+        <v>93.97470582251222</v>
       </c>
       <c r="N85">
-        <v>-84.10995932462518</v>
+        <v>-85.22870582251223</v>
       </c>
       <c r="O85">
-        <v>-20.83842714069255</v>
+        <v>-21.11559904247825</v>
       </c>
       <c r="P85">
-        <v>-63.27153218393263</v>
+        <v>-64.11310678003397</v>
       </c>
       <c r="Q85">
-        <v>-58.24153218393263</v>
+        <v>-59.08310678003397</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.239239819614344</v>
+        <v>0.2513298083402405</v>
       </c>
       <c r="T85">
-        <v>3.552303596183474</v>
+        <v>3.774322570944942</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02333550504761117</v>
+        <v>0.02305770141609199</v>
       </c>
       <c r="W85">
-        <v>0.2302974879097733</v>
+        <v>0.2303629940060855</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.09418889281434173</v>
+        <v>0.0930675964713138</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2337176842995503</v>
+        <v>0.2356176842995503</v>
       </c>
       <c r="C86">
-        <v>-303.115873266783</v>
+        <v>-308.5752289875448</v>
       </c>
       <c r="D86">
-        <v>71.41977483547407</v>
+        <v>70.70489111592953</v>
       </c>
       <c r="E86">
-        <v>199.5884479805225</v>
+        <v>204.3329199817398</v>
       </c>
       <c r="F86">
-        <v>398.535648102257</v>
+        <v>403.2801201034744</v>
       </c>
       <c r="G86">
         <v>24</v>
@@ -8321,37 +8321,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M86">
-        <v>93.97470582251221</v>
+        <v>95.09345232039925</v>
       </c>
       <c r="N86">
-        <v>-85.22870582251221</v>
+        <v>-86.34745232039926</v>
       </c>
       <c r="O86">
-        <v>-21.11559904247825</v>
+        <v>-21.39277094426394</v>
       </c>
       <c r="P86">
-        <v>-64.11310678003396</v>
+        <v>-64.95468137613531</v>
       </c>
       <c r="Q86">
-        <v>-59.08310678003396</v>
+        <v>-59.92468137613531</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2513298083402403</v>
+        <v>0.265031795562923</v>
       </c>
       <c r="T86">
-        <v>3.774322570944939</v>
+        <v>4.025944075674602</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02305770141609199</v>
+        <v>0.02278643434060856</v>
       </c>
       <c r="W86">
-        <v>0.2303629940060855</v>
+        <v>0.2304269587824845</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.09306759647131391</v>
+        <v>0.09197268357165134</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2356176842995503</v>
+        <v>0.2375176842995503</v>
       </c>
       <c r="C87">
-        <v>-308.5752289875448</v>
+        <v>-314.020415133162</v>
       </c>
       <c r="D87">
-        <v>70.70489111592953</v>
+        <v>70.00417697152972</v>
       </c>
       <c r="E87">
-        <v>204.3329199817398</v>
+        <v>209.0773919829572</v>
       </c>
       <c r="F87">
-        <v>403.2801201034744</v>
+        <v>408.0245921046917</v>
       </c>
       <c r="G87">
         <v>24</v>
@@ -8403,37 +8403,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M87">
-        <v>95.09345232039925</v>
+        <v>96.21219881828632</v>
       </c>
       <c r="N87">
-        <v>-86.34745232039926</v>
+        <v>-87.46619881828633</v>
       </c>
       <c r="O87">
-        <v>-21.39277094426394</v>
+        <v>-21.66994284604965</v>
       </c>
       <c r="P87">
-        <v>-64.95468137613531</v>
+        <v>-65.79625597223668</v>
       </c>
       <c r="Q87">
-        <v>-59.92468137613531</v>
+        <v>-60.76625597223668</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.265031795562923</v>
+        <v>0.2806912095317032</v>
       </c>
       <c r="T87">
-        <v>4.025944075674602</v>
+        <v>4.313511509651359</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02278643434060856</v>
+        <v>0.02252147580176427</v>
       </c>
       <c r="W87">
-        <v>0.2304269587824845</v>
+        <v>0.230489436005944</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.09197268357165134</v>
+        <v>0.09090323376267861</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2375176842995503</v>
+        <v>0.2394176842995503</v>
       </c>
       <c r="C88">
-        <v>-314.020415133162</v>
+        <v>-319.4518488482697</v>
       </c>
       <c r="D88">
-        <v>70.00417697152972</v>
+        <v>69.31721525763935</v>
       </c>
       <c r="E88">
-        <v>209.0773919829572</v>
+        <v>213.8218639841745</v>
       </c>
       <c r="F88">
-        <v>408.0245921046917</v>
+        <v>412.7690641059091</v>
       </c>
       <c r="G88">
         <v>24</v>
@@ -8485,37 +8485,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M88">
-        <v>96.21219881828632</v>
+        <v>97.33094531617337</v>
       </c>
       <c r="N88">
-        <v>-87.46619881828633</v>
+        <v>-88.58494531617337</v>
       </c>
       <c r="O88">
-        <v>-21.66994284604965</v>
+        <v>-21.94711474783535</v>
       </c>
       <c r="P88">
-        <v>-65.79625597223668</v>
+        <v>-66.63783056833802</v>
       </c>
       <c r="Q88">
-        <v>-60.76625597223668</v>
+        <v>-61.60783056833802</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2806912095317032</v>
+        <v>0.2987597641110651</v>
       </c>
       <c r="T88">
-        <v>4.313511509651359</v>
+        <v>4.645320087316849</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02252147580176427</v>
+        <v>0.02226260826381295</v>
       </c>
       <c r="W88">
-        <v>0.230489436005944</v>
+        <v>0.2305504769713929</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.09090323376267861</v>
+        <v>0.08985836900678579</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2394176842995503</v>
+        <v>0.2413176842995503</v>
       </c>
       <c r="C89">
-        <v>-319.4518488482697</v>
+        <v>-324.8699310626059</v>
       </c>
       <c r="D89">
-        <v>69.31721525763935</v>
+        <v>68.64360504452054</v>
       </c>
       <c r="E89">
-        <v>213.8218639841745</v>
+        <v>218.5663359853918</v>
       </c>
       <c r="F89">
-        <v>412.7690641059091</v>
+        <v>417.5135361071264</v>
       </c>
       <c r="G89">
         <v>24</v>
@@ -8567,37 +8567,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M89">
-        <v>97.33094531617337</v>
+        <v>98.44969181406042</v>
       </c>
       <c r="N89">
-        <v>-88.58494531617337</v>
+        <v>-89.70369181406042</v>
       </c>
       <c r="O89">
-        <v>-21.94711474783535</v>
+        <v>-22.22428664962105</v>
       </c>
       <c r="P89">
-        <v>-66.63783056833802</v>
+        <v>-67.47940516443937</v>
       </c>
       <c r="Q89">
-        <v>-61.60783056833802</v>
+        <v>-62.44940516443937</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2987597641110651</v>
+        <v>0.3198397444536538</v>
       </c>
       <c r="T89">
-        <v>4.645320087316849</v>
+        <v>5.032430094593253</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02226260826381295</v>
+        <v>0.0220096240789969</v>
       </c>
       <c r="W89">
-        <v>0.2305504769713929</v>
+        <v>0.2306101306421725</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.08985836900678579</v>
+        <v>0.08883725117716323</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2413176842995503</v>
+        <v>0.2432176842995503</v>
       </c>
       <c r="C90">
-        <v>-324.8699310626059</v>
+        <v>-330.2750472712929</v>
       </c>
       <c r="D90">
-        <v>68.64360504452054</v>
+        <v>67.98296083705081</v>
       </c>
       <c r="E90">
-        <v>218.5663359853918</v>
+        <v>223.3108079866092</v>
       </c>
       <c r="F90">
-        <v>417.5135361071264</v>
+        <v>422.2580081083437</v>
       </c>
       <c r="G90">
         <v>24</v>
@@ -8649,37 +8649,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M90">
-        <v>98.44969181406042</v>
+        <v>99.56843831194746</v>
       </c>
       <c r="N90">
-        <v>-89.70369181406042</v>
+        <v>-90.82243831194747</v>
       </c>
       <c r="O90">
-        <v>-22.22428664962105</v>
+        <v>-22.50145855140675</v>
       </c>
       <c r="P90">
-        <v>-67.47940516443937</v>
+        <v>-68.32097976054072</v>
       </c>
       <c r="Q90">
-        <v>-62.44940516443937</v>
+        <v>-63.29097976054072</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3198397444536538</v>
+        <v>0.3447524484948951</v>
       </c>
       <c r="T90">
-        <v>5.032430094593253</v>
+        <v>5.489923739556277</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0220096240789969</v>
+        <v>0.02176232493204188</v>
       </c>
       <c r="W90">
-        <v>0.2306101306421725</v>
+        <v>0.2306684437810245</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.08883725117716323</v>
+        <v>0.08783907981562211</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2432176842995503</v>
+        <v>0.2451176842995503</v>
       </c>
       <c r="C91">
-        <v>-330.2750472712929</v>
+        <v>-335.6675682704923</v>
       </c>
       <c r="D91">
-        <v>67.98296083705081</v>
+        <v>67.33491183906888</v>
       </c>
       <c r="E91">
-        <v>223.3108079866092</v>
+        <v>228.0552799878266</v>
       </c>
       <c r="F91">
-        <v>422.2580081083437</v>
+        <v>427.0024801095611</v>
       </c>
       <c r="G91">
         <v>24</v>
@@ -8731,37 +8731,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M91">
-        <v>99.56843831194746</v>
+        <v>100.6871848098345</v>
       </c>
       <c r="N91">
-        <v>-90.82243831194747</v>
+        <v>-91.94118480983452</v>
       </c>
       <c r="O91">
-        <v>-22.50145855140675</v>
+        <v>-22.77863045319245</v>
       </c>
       <c r="P91">
-        <v>-68.32097976054072</v>
+        <v>-69.16255435664208</v>
       </c>
       <c r="Q91">
-        <v>-63.29097976054072</v>
+        <v>-64.13255435664207</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3447524484948951</v>
+        <v>0.3746476933443847</v>
       </c>
       <c r="T91">
-        <v>5.489923739556277</v>
+        <v>6.038916113511905</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02176232493204188</v>
+        <v>0.02152052132168586</v>
       </c>
       <c r="W91">
-        <v>0.2306684437810245</v>
+        <v>0.2307254610723465</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.08783907981562211</v>
+        <v>0.0868630900398929</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2451176842995503</v>
+        <v>0.2470176842995503</v>
       </c>
       <c r="C92">
-        <v>-335.6675682704923</v>
+        <v>-341.0478508513789</v>
       </c>
       <c r="D92">
-        <v>67.33491183906888</v>
+        <v>66.6991012593995</v>
       </c>
       <c r="E92">
-        <v>228.0552799878266</v>
+        <v>232.7997519890439</v>
       </c>
       <c r="F92">
-        <v>427.0024801095611</v>
+        <v>431.7469521107785</v>
       </c>
       <c r="G92">
         <v>24</v>
@@ -8813,37 +8813,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M92">
-        <v>100.6871848098345</v>
+        <v>101.8059313077216</v>
       </c>
       <c r="N92">
-        <v>-91.94118480983452</v>
+        <v>-93.05993130772157</v>
       </c>
       <c r="O92">
-        <v>-22.77863045319245</v>
+        <v>-23.05580235497815</v>
       </c>
       <c r="P92">
-        <v>-69.16255435664208</v>
+        <v>-70.00412895274341</v>
       </c>
       <c r="Q92">
-        <v>-64.13255435664207</v>
+        <v>-64.97412895274341</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3746476933443847</v>
+        <v>0.4111863259382053</v>
       </c>
       <c r="T92">
-        <v>6.038916113511905</v>
+        <v>6.709906792791006</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02152052132168586</v>
+        <v>0.02128403207639261</v>
       </c>
       <c r="W92">
-        <v>0.2307254610723465</v>
+        <v>0.2307812252363866</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.0868630900398929</v>
+        <v>0.08590855058890512</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2470176842995503</v>
+        <v>0.2489176842995503</v>
       </c>
       <c r="C93">
-        <v>-341.0478508513789</v>
+        <v>-346.4162384551686</v>
       </c>
       <c r="D93">
-        <v>66.6991012593995</v>
+        <v>66.07518565682714</v>
       </c>
       <c r="E93">
-        <v>232.7997519890439</v>
+        <v>237.5442239902612</v>
       </c>
       <c r="F93">
-        <v>431.7469521107785</v>
+        <v>436.4914241119958</v>
       </c>
       <c r="G93">
         <v>24</v>
@@ -8895,37 +8895,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M93">
-        <v>101.8059313077216</v>
+        <v>102.9246778056086</v>
       </c>
       <c r="N93">
-        <v>-93.05993130772157</v>
+        <v>-94.17867780560861</v>
       </c>
       <c r="O93">
-        <v>-23.05580235497815</v>
+        <v>-23.33297425676385</v>
       </c>
       <c r="P93">
-        <v>-70.00412895274341</v>
+        <v>-70.84570354884477</v>
       </c>
       <c r="Q93">
-        <v>-64.97412895274341</v>
+        <v>-65.81570354884477</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4111863259382053</v>
+        <v>0.456859616680481</v>
       </c>
       <c r="T93">
-        <v>6.709906792791006</v>
+        <v>7.548645141889883</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02128403207639261</v>
+        <v>0.02105268390164921</v>
       </c>
       <c r="W93">
-        <v>0.2307812252363866</v>
+        <v>0.2308357771359911</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.08590855058890512</v>
+        <v>0.08497476199554743</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2489176842995503</v>
+        <v>0.2508176842995503</v>
       </c>
       <c r="C94">
-        <v>-346.4162384551686</v>
+        <v>-351.7730617917204</v>
       </c>
       <c r="D94">
-        <v>66.07518565682714</v>
+        <v>65.46283432149282</v>
       </c>
       <c r="E94">
-        <v>237.5442239902612</v>
+        <v>242.2886959914786</v>
       </c>
       <c r="F94">
-        <v>436.4914241119958</v>
+        <v>441.2358961132132</v>
       </c>
       <c r="G94">
         <v>24</v>
@@ -8977,37 +8977,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M94">
-        <v>102.9246778056086</v>
+        <v>104.0434243034957</v>
       </c>
       <c r="N94">
-        <v>-94.17867780560861</v>
+        <v>-95.29742430349567</v>
       </c>
       <c r="O94">
-        <v>-23.33297425676385</v>
+        <v>-23.61014615854955</v>
       </c>
       <c r="P94">
-        <v>-70.84570354884477</v>
+        <v>-71.68727814494612</v>
       </c>
       <c r="Q94">
-        <v>-65.81570354884477</v>
+        <v>-66.65727814494612</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.456859616680481</v>
+        <v>0.5155824190634068</v>
       </c>
       <c r="T94">
-        <v>7.548645141889883</v>
+        <v>8.627023019302726</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02105268390164921</v>
+        <v>0.02082631095647018</v>
       </c>
       <c r="W94">
-        <v>0.2308357771359911</v>
+        <v>0.2308891558764644</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.08497476199554743</v>
+        <v>0.08406105487731574</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2508176842995503</v>
+        <v>0.2527176842995503</v>
       </c>
       <c r="C95">
-        <v>-351.7730617917204</v>
+        <v>-357.118639424058</v>
       </c>
       <c r="D95">
-        <v>65.46283432149282</v>
+        <v>64.86172869037249</v>
       </c>
       <c r="E95">
-        <v>242.2886959914786</v>
+        <v>247.033167992696</v>
       </c>
       <c r="F95">
-        <v>441.2358961132132</v>
+        <v>445.9803681144305</v>
       </c>
       <c r="G95">
         <v>24</v>
@@ -9059,37 +9059,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M95">
-        <v>104.0434243034957</v>
+        <v>105.1621708013827</v>
       </c>
       <c r="N95">
-        <v>-95.29742430349567</v>
+        <v>-96.41617080138272</v>
       </c>
       <c r="O95">
-        <v>-23.61014615854955</v>
+        <v>-23.88731806033525</v>
       </c>
       <c r="P95">
-        <v>-71.68727814494612</v>
+        <v>-72.52885274104747</v>
       </c>
       <c r="Q95">
-        <v>-66.65727814494612</v>
+        <v>-67.49885274104747</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5155824190634068</v>
+        <v>0.5938794889073081</v>
       </c>
       <c r="T95">
-        <v>8.627023019302726</v>
+        <v>10.06486018918651</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02082631095647018</v>
+        <v>0.02060475445693327</v>
       </c>
       <c r="W95">
-        <v>0.2308891558764644</v>
+        <v>0.2309413988990552</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.08406105487731574</v>
+        <v>0.08316678833606772</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2527176842995503</v>
+        <v>0.2546176842995503</v>
       </c>
       <c r="C96">
-        <v>-357.118639424058</v>
+        <v>-362.453278320982</v>
       </c>
       <c r="D96">
-        <v>64.86172869037249</v>
+        <v>64.2715617946659</v>
       </c>
       <c r="E96">
-        <v>247.033167992696</v>
+        <v>251.7776399939133</v>
       </c>
       <c r="F96">
-        <v>445.9803681144305</v>
+        <v>450.7248401156479</v>
       </c>
       <c r="G96">
         <v>24</v>
@@ -9141,37 +9141,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M96">
-        <v>105.1621708013827</v>
+        <v>106.2809172992698</v>
       </c>
       <c r="N96">
-        <v>-96.41617080138272</v>
+        <v>-97.53491729926978</v>
       </c>
       <c r="O96">
-        <v>-23.88731806033525</v>
+        <v>-24.16448996212095</v>
       </c>
       <c r="P96">
-        <v>-72.52885274104747</v>
+        <v>-73.37042733714883</v>
       </c>
       <c r="Q96">
-        <v>-67.49885274104747</v>
+        <v>-68.34042733714882</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5938794889073081</v>
+        <v>0.7034953866887701</v>
       </c>
       <c r="T96">
-        <v>10.06486018918651</v>
+        <v>12.07783222702382</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02060475445693327</v>
+        <v>0.02038786230475502</v>
       </c>
       <c r="W96">
-        <v>0.2309413988990552</v>
+        <v>0.2309925420685388</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.08316678833606772</v>
+        <v>0.08229134845884589</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2546176842995503</v>
+        <v>0.2565176842995503</v>
       </c>
       <c r="C97">
-        <v>-362.453278320982</v>
+        <v>-367.7772743797827</v>
       </c>
       <c r="D97">
-        <v>64.2715617946659</v>
+        <v>63.69203773708247</v>
       </c>
       <c r="E97">
-        <v>251.7776399939133</v>
+        <v>256.5221119951307</v>
       </c>
       <c r="F97">
-        <v>450.7248401156479</v>
+        <v>455.4693121168652</v>
       </c>
       <c r="G97">
         <v>24</v>
@@ -9223,37 +9223,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M97">
-        <v>106.2809172992698</v>
+        <v>107.3996637971568</v>
       </c>
       <c r="N97">
-        <v>-97.53491729926978</v>
+        <v>-98.65366379715684</v>
       </c>
       <c r="O97">
-        <v>-24.16448996212095</v>
+        <v>-24.44166186390666</v>
       </c>
       <c r="P97">
-        <v>-73.37042733714883</v>
+        <v>-74.21200193325018</v>
       </c>
       <c r="Q97">
-        <v>-68.34042733714882</v>
+        <v>-69.18200193325018</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7034953866887701</v>
+        <v>0.8679192333609629</v>
       </c>
       <c r="T97">
-        <v>12.07783222702382</v>
+        <v>15.09729028377979</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02038786230475502</v>
+        <v>0.02017548873908049</v>
       </c>
       <c r="W97">
-        <v>0.2309925420685388</v>
+        <v>0.2310426197553248</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.08229134845884589</v>
+        <v>0.08143414691239959</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2565176842995503</v>
+        <v>0.2584176842995503</v>
       </c>
       <c r="C98">
-        <v>-367.7772743797827</v>
+        <v>-373.0909129209289</v>
       </c>
       <c r="D98">
-        <v>63.69203773708247</v>
+        <v>63.1228711971536</v>
       </c>
       <c r="E98">
-        <v>256.5221119951306</v>
+        <v>261.2665839963479</v>
       </c>
       <c r="F98">
-        <v>455.4693121168652</v>
+        <v>460.2137841180825</v>
       </c>
       <c r="G98">
         <v>24</v>
@@ -9305,37 +9305,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M98">
-        <v>107.3996637971568</v>
+        <v>108.5184102950439</v>
       </c>
       <c r="N98">
-        <v>-98.65366379715682</v>
+        <v>-99.77241029504387</v>
       </c>
       <c r="O98">
-        <v>-24.44166186390665</v>
+        <v>-24.71883376569235</v>
       </c>
       <c r="P98">
-        <v>-74.21200193325018</v>
+        <v>-75.05357652935152</v>
       </c>
       <c r="Q98">
-        <v>-69.18200193325018</v>
+        <v>-70.02357652935152</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8679192333609607</v>
+        <v>1.141958977814615</v>
       </c>
       <c r="T98">
-        <v>15.09729028377975</v>
+        <v>20.129720378373</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02017548873908049</v>
+        <v>0.01996749400981162</v>
       </c>
       <c r="W98">
-        <v>0.2310426197553248</v>
+        <v>0.2310916649124864</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.08143414691239959</v>
+        <v>0.08059461962464287</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2584176842995503</v>
+        <v>0.2603176842995503</v>
       </c>
       <c r="C99">
-        <v>-373.0909129209289</v>
+        <v>-378.3944691564657</v>
       </c>
       <c r="D99">
-        <v>63.1228711971536</v>
+        <v>62.5637869628342</v>
       </c>
       <c r="E99">
-        <v>261.2665839963479</v>
+        <v>266.0110559975653</v>
       </c>
       <c r="F99">
-        <v>460.2137841180825</v>
+        <v>464.9582561192998</v>
       </c>
       <c r="G99">
         <v>24</v>
@@ -9387,37 +9387,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M99">
-        <v>108.5184102950439</v>
+        <v>109.6371567929309</v>
       </c>
       <c r="N99">
-        <v>-99.77241029504387</v>
+        <v>-100.8911567929309</v>
       </c>
       <c r="O99">
-        <v>-24.71883376569235</v>
+        <v>-24.99600566747805</v>
       </c>
       <c r="P99">
-        <v>-75.05357652935152</v>
+        <v>-75.89515112545287</v>
       </c>
       <c r="Q99">
-        <v>-70.02357652935152</v>
+        <v>-70.86515112545287</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.141958977814615</v>
+        <v>1.690038466721922</v>
       </c>
       <c r="T99">
-        <v>20.129720378373</v>
+        <v>30.19458056755949</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01996749400981162</v>
+        <v>0.01976374407093599</v>
       </c>
       <c r="W99">
-        <v>0.2310916649124864</v>
+        <v>0.2311397091480733</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.08059461962464287</v>
+        <v>0.07977222554684049</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2603176842995503</v>
+        <v>0.2622176842995503</v>
       </c>
       <c r="C100">
-        <v>-378.3944691564657</v>
+        <v>-383.6882086337404</v>
       </c>
       <c r="D100">
-        <v>62.5637869628342</v>
+        <v>62.01451948677683</v>
       </c>
       <c r="E100">
-        <v>266.0110559975653</v>
+        <v>270.7555279987827</v>
       </c>
       <c r="F100">
-        <v>464.9582561192998</v>
+        <v>469.7027281205172</v>
       </c>
       <c r="G100">
         <v>24</v>
@@ -9469,37 +9469,37 @@
         <v>8.745999999999999</v>
       </c>
       <c r="M100">
-        <v>109.6371567929309</v>
+        <v>110.755903290818</v>
       </c>
       <c r="N100">
-        <v>-100.8911567929309</v>
+        <v>-102.009903290818</v>
       </c>
       <c r="O100">
-        <v>-24.99600566747805</v>
+        <v>-25.27317756926375</v>
       </c>
       <c r="P100">
-        <v>-75.89515112545287</v>
+        <v>-76.73672572155422</v>
       </c>
       <c r="Q100">
-        <v>-70.86515112545287</v>
+        <v>-71.70672572155422</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.690038466721922</v>
+        <v>3.334276933443843</v>
       </c>
       <c r="T100">
-        <v>30.19458056755949</v>
+        <v>60.38916113511899</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01976374407093599</v>
+        <v>0.01956411029244169</v>
       </c>
       <c r="W100">
-        <v>0.2311397091480733</v>
+        <v>0.2311867827930423</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.07977222554684049</v>
+        <v>0.07896644549081178</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2622176842995503</v>
-      </c>
-      <c r="C101">
-        <v>-383.6882086337404</v>
-      </c>
-      <c r="D101">
-        <v>62.01451948677683</v>
-      </c>
-      <c r="E101">
-        <v>270.7555279987827</v>
-      </c>
-      <c r="F101">
-        <v>469.7027281205172</v>
-      </c>
-      <c r="G101">
-        <v>24</v>
-      </c>
-      <c r="H101">
-        <v>275.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>13.776</v>
-      </c>
-      <c r="K101">
-        <v>5.03</v>
-      </c>
-      <c r="L101">
-        <v>8.745999999999999</v>
-      </c>
-      <c r="M101">
-        <v>110.755903290818</v>
-      </c>
-      <c r="N101">
-        <v>-102.009903290818</v>
-      </c>
-      <c r="O101">
-        <v>-25.27317756926375</v>
-      </c>
-      <c r="P101">
-        <v>-76.73672572155422</v>
-      </c>
-      <c r="Q101">
-        <v>-71.70672572155422</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.334276933443843</v>
-      </c>
-      <c r="T101">
-        <v>60.38916113511899</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01956411029244169</v>
-      </c>
-      <c r="W101">
-        <v>0.2311867827930423</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07896644549081178</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
